--- a/data/ams_weekly_data/White_Mulberry/ads_report_week23.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week23.xlsx
@@ -507,7 +507,7 @@
         <v>19</v>
       </c>
       <c r="F3" t="n">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -535,7 +535,7 @@
         <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>1347</v>
+        <v>1340</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -563,7 +563,7 @@
         <v>14</v>
       </c>
       <c r="F5" t="n">
-        <v>1816</v>
+        <v>1814</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -591,7 +591,7 @@
         <v>14</v>
       </c>
       <c r="F6" t="n">
-        <v>3484</v>
+        <v>3477</v>
       </c>
       <c r="G6" t="n">
         <v>7117.8</v>
@@ -647,7 +647,7 @@
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -815,7 +815,7 @@
         <v>18</v>
       </c>
       <c r="F14" t="n">
-        <v>3695</v>
+        <v>3694</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -843,7 +843,7 @@
         <v>5</v>
       </c>
       <c r="F15" t="n">
-        <v>2837</v>
+        <v>2833</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -955,7 +955,7 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1039,7 +1039,7 @@
         <v>6</v>
       </c>
       <c r="F22" t="n">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1095,7 +1095,7 @@
         <v>26</v>
       </c>
       <c r="F24" t="n">
-        <v>3818</v>
+        <v>3793</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1123,7 +1123,7 @@
         <v>27</v>
       </c>
       <c r="F25" t="n">
-        <v>3797</v>
+        <v>3770</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1151,7 +1151,7 @@
         <v>7</v>
       </c>
       <c r="F26" t="n">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1291,7 +1291,7 @@
         <v>18</v>
       </c>
       <c r="F31" t="n">
-        <v>3933</v>
+        <v>3895</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
         <v>10</v>
       </c>
       <c r="F32" t="n">
-        <v>2288</v>
+        <v>2281</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1347,7 +1347,7 @@
         <v>6</v>
       </c>
       <c r="F33" t="n">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1375,7 +1375,7 @@
         <v>20</v>
       </c>
       <c r="F34" t="n">
-        <v>6765</v>
+        <v>6730</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="F35" t="n">
-        <v>902</v>
+        <v>897</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1431,7 +1431,7 @@
         <v>10</v>
       </c>
       <c r="F36" t="n">
-        <v>4570</v>
+        <v>4565</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1459,7 +1459,7 @@
         <v>15</v>
       </c>
       <c r="F37" t="n">
-        <v>1800</v>
+        <v>1797</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1487,7 +1487,7 @@
         <v>25</v>
       </c>
       <c r="F38" t="n">
-        <v>6783</v>
+        <v>6685</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1543,7 +1543,7 @@
         <v>36</v>
       </c>
       <c r="F40" t="n">
-        <v>2778</v>
+        <v>2737</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1571,7 +1571,7 @@
         <v>31</v>
       </c>
       <c r="F41" t="n">
-        <v>4619</v>
+        <v>4577</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1599,13 +1599,13 @@
         <v>12</v>
       </c>
       <c r="F42" t="n">
-        <v>1080</v>
+        <v>1075</v>
       </c>
       <c r="G42" t="n">
-        <v>7202.54</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1627,7 +1627,7 @@
         <v>8</v>
       </c>
       <c r="F43" t="n">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1655,7 +1655,7 @@
         <v>51</v>
       </c>
       <c r="F44" t="n">
-        <v>5792</v>
+        <v>5767</v>
       </c>
       <c r="G44" t="n">
         <v>7202.54</v>
@@ -1683,7 +1683,7 @@
         <v>40</v>
       </c>
       <c r="F45" t="n">
-        <v>2258</v>
+        <v>2255</v>
       </c>
       <c r="G45" t="n">
         <v>7202.54</v>
@@ -1711,7 +1711,7 @@
         <v>25</v>
       </c>
       <c r="F46" t="n">
-        <v>2449</v>
+        <v>2419</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1795,7 +1795,7 @@
         <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1823,7 +1823,7 @@
         <v>8</v>
       </c>
       <c r="F50" t="n">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1851,7 +1851,7 @@
         <v>5</v>
       </c>
       <c r="F51" t="n">
-        <v>1207</v>
+        <v>1202</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
         <v>14</v>
       </c>
       <c r="F52" t="n">
-        <v>1796</v>
+        <v>1792</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -2019,7 +2019,7 @@
         <v>11</v>
       </c>
       <c r="F57" t="n">
-        <v>1733</v>
+        <v>1727</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -2075,7 +2075,7 @@
         <v>9</v>
       </c>
       <c r="F59" t="n">
-        <v>1506</v>
+        <v>1500</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -2103,7 +2103,7 @@
         <v>16</v>
       </c>
       <c r="F60" t="n">
-        <v>2139</v>
+        <v>2133</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2159,7 +2159,7 @@
         <v>11</v>
       </c>
       <c r="F62" t="n">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2187,7 +2187,7 @@
         <v>17</v>
       </c>
       <c r="F63" t="n">
-        <v>1709</v>
+        <v>1704</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2215,7 +2215,7 @@
         <v>42</v>
       </c>
       <c r="F64" t="n">
-        <v>1509</v>
+        <v>1505</v>
       </c>
       <c r="G64" t="n">
         <v>2795.76</v>
@@ -2243,7 +2243,7 @@
         <v>15</v>
       </c>
       <c r="F65" t="n">
-        <v>1852</v>
+        <v>1850</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2271,7 +2271,7 @@
         <v>20</v>
       </c>
       <c r="F66" t="n">
-        <v>937</v>
+        <v>926</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2299,7 +2299,7 @@
         <v>12</v>
       </c>
       <c r="F67" t="n">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="G67" t="n">
         <v>2795.76</v>
@@ -2327,7 +2327,7 @@
         <v>33</v>
       </c>
       <c r="F68" t="n">
-        <v>2688</v>
+        <v>2674</v>
       </c>
       <c r="G68" t="n">
         <v>5591.52</v>
@@ -2355,7 +2355,7 @@
         <v>11</v>
       </c>
       <c r="F69" t="n">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2411,7 +2411,7 @@
         <v>11</v>
       </c>
       <c r="F71" t="n">
-        <v>4142</v>
+        <v>4132</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2467,7 +2467,7 @@
         <v>7</v>
       </c>
       <c r="F73" t="n">
-        <v>2145</v>
+        <v>2143</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2607,7 +2607,7 @@
         <v>17</v>
       </c>
       <c r="F78" t="n">
-        <v>5866</v>
+        <v>5855</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2663,7 +2663,7 @@
         <v>10</v>
       </c>
       <c r="F80" t="n">
-        <v>1741</v>
+        <v>1726</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2691,7 +2691,7 @@
         <v>16</v>
       </c>
       <c r="F81" t="n">
-        <v>5897</v>
+        <v>5896</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>30</v>
       </c>
       <c r="F83" t="n">
-        <v>5921</v>
+        <v>5908</v>
       </c>
       <c r="G83" t="n">
         <v>4659.32</v>
@@ -2971,7 +2971,7 @@
         <v>5</v>
       </c>
       <c r="F91" t="n">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -3055,7 +3055,7 @@
         <v>4</v>
       </c>
       <c r="F94" t="n">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -3111,7 +3111,7 @@
         <v>5</v>
       </c>
       <c r="F96" t="n">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -3139,7 +3139,7 @@
         <v>1</v>
       </c>
       <c r="F97" t="n">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -3195,7 +3195,7 @@
         <v>15</v>
       </c>
       <c r="F99" t="n">
-        <v>1055</v>
+        <v>1048</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3223,7 +3223,7 @@
         <v>12</v>
       </c>
       <c r="F100" t="n">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3251,7 +3251,7 @@
         <v>12</v>
       </c>
       <c r="F101" t="n">
-        <v>2081</v>
+        <v>2078</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3391,7 +3391,7 @@
         <v>19</v>
       </c>
       <c r="F106" t="n">
-        <v>2255</v>
+        <v>2253</v>
       </c>
       <c r="G106" t="n">
         <v>617.8</v>
@@ -3559,7 +3559,7 @@
         <v>19</v>
       </c>
       <c r="F112" t="n">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="G112" t="n">
         <v>1636.44</v>
@@ -3615,7 +3615,7 @@
         <v>21</v>
       </c>
       <c r="F114" t="n">
-        <v>8481</v>
+        <v>8457</v>
       </c>
       <c r="G114" t="n">
         <v>12712.71</v>
@@ -3635,7 +3635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3684,22 +3684,22 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>WM_Monitor Arm_High Selling_SD_VRM_7,14,30</t>
+          <t>L-Shape - SD Views RMKTNG - Apr'26 a30650</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>123.09</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>3573</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -3712,22 +3712,22 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WM_Monitor Arm_High Selling_SD_VRM_7,14,30</t>
+          <t>L-Shape - SD Views RMKTNG - Apr'26 a30650</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0BFVNS8HS</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>118.76</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>5149</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -3740,22 +3740,22 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WM_Monitor Arm_High Selling_SD_VRM_7,14,30</t>
+          <t>L-Shape - SD Views RMKTNG - Apr'26 a30650</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>84.45999999999999</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2306</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -3768,27 +3768,391 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
+          <t>L-Shape SD Purchase RMKTNG - Apr'26 f19c32</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>B0BFVMDJ2K</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>L-Shape SD Purchase RMKTNG - Apr'26 f19c32</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>B0BFVNS8HS</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>L-Shape SD Purchase RMKTNG - Apr'26 f19c32</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>B0BFW59TRG</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SD_VRM_Top Selling ASINs 8c3467</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>B0CPFS24ML</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SD_VR_Z Shape Desk_BMC</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>B0CPFS24ML</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>WM_Monitor Arm_High Selling_SD_VRM_7,14,30</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>123.09</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3573</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>WM_Monitor Arm_High Selling_SD_VRM_7,14,30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>B0DB5W4TCP</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>118.76</v>
+      </c>
+      <c r="E11" t="n">
+        <v>15</v>
+      </c>
+      <c r="F11" t="n">
+        <v>5149</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>WM_Monitor Arm_High Selling_SD_VRM_7,14,30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>B0DP2VVRND</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>WM_Monitor Arm_High Selling_SD_VRM_7,14,30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>B0DP2WC5VW</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>WM_Monitor Arm_High Selling_SD_VRM_7,14,30</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>B0DP2Z5DQ9</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>84.45999999999999</v>
+      </c>
+      <c r="E14" t="n">
+        <v>6</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2306</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>WM_Monitor Arm_High Selling_SD_VRM_7,14,30</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>B0DP32F346</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D15" t="n">
         <v>136.82</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E15" t="n">
         <v>15</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F15" t="n">
         <v>4776</v>
       </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>WM_POS Stand_High Selling_VRM_7,14,30</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>B0FN4FPJ83</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>WM_TV Wall_High Selling_VRM_7,14,30</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>B0FN4D3C89</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>WM_TV Wall_High Selling_VRM_7,14,30</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>B0FN4DSQ6P</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4064,13 +4428,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="E8" t="n">
         <v>59</v>
       </c>
       <c r="F8" t="n">
-        <v>124.84</v>
+        <v>124.715</v>
       </c>
       <c r="G8" t="n">
         <v>3558.9</v>
@@ -4097,13 +4461,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="E9" t="n">
         <v>59</v>
       </c>
       <c r="F9" t="n">
-        <v>124.84</v>
+        <v>124.715</v>
       </c>
       <c r="G9" t="n">
         <v>3558.9</v>
@@ -4163,7 +4527,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1488</v>
+        <v>1483</v>
       </c>
       <c r="E11" t="n">
         <v>20</v>
@@ -4196,7 +4560,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3392</v>
+        <v>3376</v>
       </c>
       <c r="E12" t="n">
         <v>25</v>
@@ -4229,7 +4593,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E13" t="n">
         <v>4</v>
@@ -4262,7 +4626,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E14" t="n">
         <v>4</v>
@@ -4295,7 +4659,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E15" t="n">
         <v>4</v>
@@ -4328,7 +4692,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E16" t="n">
         <v>4</v>
@@ -4361,7 +4725,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E17" t="n">
         <v>4</v>
@@ -4394,7 +4758,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E18" t="n">
         <v>4</v>
@@ -4427,7 +4791,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2463</v>
+        <v>2447</v>
       </c>
       <c r="E19" t="n">
         <v>16</v>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week23.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week23.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H114"/>
+  <dimension ref="A1:H126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,17 +469,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>84.56999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>194</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -497,17 +497,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0BFVNS8HS</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>330.89</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1781</v>
+        <v>16</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -525,17 +525,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>45.87</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1340</v>
+        <v>210</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -548,22 +548,22 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Camb-B0BFVMDJ2K-L Shaped -Exact &amp; Phrase(1)-SP</t>
+          <t>Camb - Multi Asin-Defensive</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>290.59</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>1814</v>
+        <v>431</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -576,50 +576,50 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Camb-B0BFW59TRG-L-Shape-Phrase-Exact-SP</t>
+          <t>Camb - Multi Asin-Defensive</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>332.08</v>
+        <v>468.1799999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F6" t="n">
-        <v>3477</v>
+        <v>2489</v>
       </c>
       <c r="G6" t="n">
-        <v>7117.8</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Camb-B0CPT3Q25C - Motorized-SP-PT</t>
+          <t>Camb - Multi Asin-Defensive</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>286.71</v>
+        <v>98.94999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v>809</v>
+        <v>1823</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -632,7 +632,7 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Camb-L shaped-SP- B0BFVMDJ2K /B0BFWD6SNF -BM</t>
+          <t>Camb-B0BFVMDJ2K-L Shaped -Exact &amp; Phrase(1)-SP</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -641,13 +641,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>269.01</v>
+        <v>1204.02</v>
       </c>
       <c r="E8" t="n">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="F8" t="n">
-        <v>742</v>
+        <v>10841</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -660,50 +660,50 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Camb-L shaped-SP- B0BFVMDJ2K /B0BFWD6SNF -BM</t>
+          <t>Camb-B0BFW59TRG-L-Shape-Phrase-Exact-SP</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>92.70999999999999</v>
+        <v>976.74</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="F9" t="n">
-        <v>1152</v>
+        <v>9974</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>7117.8</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Camb-Lshape- B0BFVMDJ2K/ B0BFWD6SNF - BM</t>
+          <t>Camb-B0CPT3Q25C - Motorized-SP-PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>300.98</v>
+        <v>854.92</v>
       </c>
       <c r="E10" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F10" t="n">
-        <v>836</v>
+        <v>1494</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -716,22 +716,22 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Camb-Lshape- B0BFVMDJ2K/ B0BFWD6SNF - BM</t>
+          <t>Camb-L shaped-SP- B0BFVMDJ2K /B0BFWD6SNF -BM</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>883.8099999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F11" t="n">
-        <v>145</v>
+        <v>3950</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -744,22 +744,22 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Camb-Lshape- B0BFVMDJ2K/ B0BFWD6SNF - PT</t>
+          <t>Camb-L shaped-SP- B0BFVMDJ2K /B0BFWD6SNF -BM</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>66.12</v>
+        <v>496.21</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F12" t="n">
-        <v>107</v>
+        <v>6069</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -772,22 +772,22 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Camb-Lshape- B0BFVMDJ2K/ B0BFWD6SNF - PT</t>
+          <t>Camb-Lshape- B0BFVMDJ2K/ B0BFWD6SNF - BM</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1030.08</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="F13" t="n">
-        <v>61</v>
+        <v>8449</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -800,22 +800,22 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Camb-Lshape- B0BFVMDJ2K/ B0BFWD6SNF - Phrase</t>
+          <t>Camb-Lshape- B0BFVMDJ2K/ B0BFWD6SNF - BM</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>361.09</v>
+        <v>269.55</v>
       </c>
       <c r="E14" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F14" t="n">
-        <v>3694</v>
+        <v>7321</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -828,22 +828,22 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Camb-Lshape- B0BFVMDJ2K/ B0BFWD6SNF - Phrase</t>
+          <t>Camb-Lshape- B0BFVMDJ2K/ B0BFWD6SNF - PT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>104.22</v>
+        <v>310.19</v>
       </c>
       <c r="E15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F15" t="n">
-        <v>2833</v>
+        <v>870</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -856,7 +856,7 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Camb-SP- L Shaped-B0BFWD6SNF-Exact &amp; Phrase(2)</t>
+          <t>Camb-Lshape- B0BFVMDJ2K/ B0BFWD6SNF - PT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -865,13 +865,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>276.2</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F16" t="n">
-        <v>53</v>
+        <v>1347</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -884,22 +884,22 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Camb-SP-B0BFVNS8HS -L-Shape-Exact-phrase</t>
+          <t>Camb-Lshape- B0BFVMDJ2K/ B0BFWD6SNF - Phrase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0BFVNS8HS</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>63.37</v>
+        <v>812.5799999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="F17" t="n">
-        <v>365</v>
+        <v>10276</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -912,22 +912,22 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Camb-SP-Branded</t>
+          <t>Camb-Lshape- B0BFVMDJ2K/ B0BFWD6SNF - Phrase</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>283.15</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F18" t="n">
-        <v>75</v>
+        <v>7295</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -940,22 +940,22 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Camb-SP-Branded</t>
+          <t>Camb-SP- L Shaped-B0BFWD6SNF-Exact &amp; Phrase(2)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0BFVNS8HS</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>15.53</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>564</v>
+        <v>247</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -968,22 +968,22 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Camb-SP-Branded</t>
+          <t>Camb-SP-B0BFVNS8HS -L-Shape-Exact-phrase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0BFVNS8HS</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>150.3</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F20" t="n">
-        <v>70</v>
+        <v>2429</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>93.41</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F21" t="n">
-        <v>77</v>
+        <v>459</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1029,17 +1029,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0BFVNS8HS</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>71.54000000000001</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>523</v>
+        <v>2101</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1057,17 +1057,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>40.31</v>
+        <v>17.09</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>352</v>
+        <v>291</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1080,22 +1080,22 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-B0BFVMDJ2K/B0BFWD6SNF- Exact/Phrase</t>
+          <t>Camb-SP-Branded</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>607.13</v>
+        <v>125.16</v>
       </c>
       <c r="E24" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F24" t="n">
-        <v>3793</v>
+        <v>687</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1108,50 +1108,50 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-B0BFWD6SNF - Broad</t>
+          <t>Camb-SP-Branded</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>271.74</v>
+        <v>289.13</v>
       </c>
       <c r="E25" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F25" t="n">
-        <v>3770</v>
+        <v>1553</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>11016.1</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-CDesk-Multiple Asin- PT</t>
+          <t>Camb-SP-Branded</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>188.32</v>
+        <v>104.2</v>
       </c>
       <c r="E26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F26" t="n">
-        <v>879</v>
+        <v>779</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1164,7 +1164,7 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multi Asin- AT</t>
+          <t>Camb-SP-Lshape-B0BFVMDJ2K/B0BFWD6SNF- Exact/Phrase</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1173,13 +1173,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>263.02</v>
+        <v>1565.55</v>
       </c>
       <c r="E27" t="n">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="F27" t="n">
-        <v>960</v>
+        <v>11853</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1192,35 +1192,35 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multi Asin- AT</t>
+          <t>Camb-SP-Lshape-B0BFWD6SNF - Broad</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0BFVNS8HS</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>510.59</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="F28" t="n">
-        <v>40</v>
+        <v>6835</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>28428.8</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multi Asin- AT</t>
+          <t>Camb-SP-Lshape-CDesk-Multiple Asin- PT</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1229,13 +1229,13 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>89.8</v>
+        <v>399.75</v>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F29" t="n">
-        <v>1095</v>
+        <v>2631</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1253,17 +1253,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>93.31999999999999</v>
+        <v>263.02</v>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F30" t="n">
-        <v>1171</v>
+        <v>960</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1276,22 +1276,22 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multiple Asins- Exact 01</t>
+          <t>Camb-SP-Lshape-Multi Asin- AT</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFVNS8HS</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>400.91</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>3895</v>
+        <v>40</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1304,7 +1304,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multiple Asins- Exact 01</t>
+          <t>Camb-SP-Lshape-Multi Asin- AT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1313,13 +1313,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>215.33</v>
+        <v>89.8</v>
       </c>
       <c r="E32" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F32" t="n">
-        <v>2281</v>
+        <v>1095</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1332,22 +1332,22 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multiple Asins- Exact/Phrase</t>
+          <t>Camb-SP-Lshape-Multi Asin- AT</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>77.45</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F33" t="n">
-        <v>872</v>
+        <v>1171</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1360,22 +1360,22 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multiple Asins- Exact/Phrase</t>
+          <t>Camb-SP-Lshape-Multiple Asins- Exact 01</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>409.0600000000001</v>
+        <v>1382.91</v>
       </c>
       <c r="E34" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F34" t="n">
-        <v>6730</v>
+        <v>19479</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1388,22 +1388,22 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multiple Asins- Exact/Phrase</t>
+          <t>Camb-SP-Lshape-Multiple Asins- Exact 01</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>41.56</v>
+        <v>335.05</v>
       </c>
       <c r="E35" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="F35" t="n">
-        <v>897</v>
+        <v>4353</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1416,22 +1416,22 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Camb-SP-Motorized Desk- B0CPT3Q25C- Exact</t>
+          <t>Camb-SP-Lshape-Multiple Asins- Exact/Phrase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>322.17</v>
+        <v>150.65</v>
       </c>
       <c r="E36" t="n">
         <v>10</v>
       </c>
       <c r="F36" t="n">
-        <v>4565</v>
+        <v>1371</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1444,50 +1444,50 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Camb-SP-Motorized Desk-B0CPT3Q25C - PT01</t>
+          <t>Camb-SP-Lshape-Multiple Asins- Exact/Phrase</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>313.97</v>
+        <v>1039.42</v>
       </c>
       <c r="E37" t="n">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="F37" t="n">
-        <v>1797</v>
+        <v>18340</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>7075.42</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Camb-SP-Motorized Desk-B0CPT3Q25C- Exact</t>
+          <t>Camb-SP-Lshape-Multiple Asins- Exact/Phrase</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>643.64</v>
+        <v>198.65</v>
       </c>
       <c r="E38" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F38" t="n">
-        <v>6685</v>
+        <v>2984</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1500,22 +1500,22 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Camb-SP-Zshape-B0CPFS24ML- CT ref</t>
+          <t>Camb-SP-Motorized Desk- B0CPT3Q25C- Exact</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>399.3100000000001</v>
+        <v>1036.11</v>
       </c>
       <c r="E39" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F39" t="n">
-        <v>2015</v>
+        <v>8976</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1528,22 +1528,22 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Camb-SP-Zshape-B0CPFS24ML- PT</t>
+          <t>Camb-SP-Motorized Desk-B0CPT3Q25C - PT01</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>554.9300000000001</v>
+        <v>971.0700000000001</v>
       </c>
       <c r="E40" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="F40" t="n">
-        <v>2737</v>
+        <v>5559</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1556,22 +1556,22 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Camb-SP-Zshape-B0CPFS24ML- Phrase</t>
+          <t>Camb-SP-Motorized Desk-B0CPT3Q25C- Exact</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>321.39</v>
+        <v>1717.93</v>
       </c>
       <c r="E41" t="n">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="F41" t="n">
-        <v>4577</v>
+        <v>16289</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1584,7 +1584,7 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Camb-SP-Zshape-B0CPFS24ML-PT01</t>
+          <t>Camb-SP-Zshape-B0CPFS24ML- CT ref</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1593,41 +1593,41 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>253.51</v>
+        <v>1127.24</v>
       </c>
       <c r="E42" t="n">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F42" t="n">
-        <v>1075</v>
+        <v>5609</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>7202.54</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Camb-SP-stand desk- B0DQ1NV8D2- PT</t>
+          <t>Camb-SP-Zshape-B0CPFS24ML- PT</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>283.84</v>
+        <v>1329.11</v>
       </c>
       <c r="E43" t="n">
-        <v>8</v>
+        <v>85</v>
       </c>
       <c r="F43" t="n">
-        <v>602</v>
+        <v>6387</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1640,7 +1640,7 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Camb-Zshape-Gaming- B0CPFS24ML-Phrase/Exact</t>
+          <t>Camb-SP-Zshape-B0CPFS24ML- Phrase</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1649,26 +1649,26 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>517.79</v>
+        <v>1133.71</v>
       </c>
       <c r="E44" t="n">
-        <v>51</v>
+        <v>95</v>
       </c>
       <c r="F44" t="n">
-        <v>5767</v>
+        <v>13216</v>
       </c>
       <c r="G44" t="n">
-        <v>7202.54</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SP CT PT_B0CPFS24ML_Gaming</t>
+          <t>Camb-SP-Zshape-B0CPFS24ML-PT01</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1677,41 +1677,41 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>309.41</v>
+        <v>595.46</v>
       </c>
       <c r="E45" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="F45" t="n">
-        <v>2255</v>
+        <v>2450</v>
       </c>
       <c r="G45" t="n">
-        <v>7202.54</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SP KT_B0CPFS24ML_Manual_Gaming</t>
+          <t>Camb-SP-stand desk- B0DQ1NV8D2- PT</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>460.25</v>
+        <v>827.4299999999999</v>
       </c>
       <c r="E46" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F46" t="n">
-        <v>2419</v>
+        <v>3145</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1724,78 +1724,78 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SP_KT_L shape Non Performing Ex</t>
+          <t>Camb-Zshape-Gaming- B0CPFS24ML-Phrase/Exact</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.09</v>
+        <v>1655.8</v>
       </c>
       <c r="E47" t="n">
+        <v>161</v>
+      </c>
+      <c r="F47" t="n">
+        <v>22289</v>
+      </c>
+      <c r="G47" t="n">
+        <v>7202.54</v>
+      </c>
+      <c r="H47" t="n">
         <v>1</v>
-      </c>
-      <c r="F47" t="n">
-        <v>728</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SP_KT_L shape Non Performing Ex</t>
+          <t>SP CT PT_B0CPFS24ML_Gaming</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>21.4</v>
+        <v>1037.06</v>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>112</v>
       </c>
       <c r="F48" t="n">
-        <v>1103</v>
+        <v>9445</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>14405.08</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SP_KT_L shape Non Performing Ex</t>
+          <t>SP KT_B0CPFS24ML_Manual_Gaming</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.79</v>
+        <v>1178.62</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="F49" t="n">
-        <v>509</v>
+        <v>5927</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1808,7 +1808,7 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SP_PT_L shape Non Performing PT</t>
+          <t>SP_KT_L shape Non Performing Ex</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1817,13 +1817,13 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>169.17</v>
+        <v>33.18</v>
       </c>
       <c r="E50" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F50" t="n">
-        <v>479</v>
+        <v>1286</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1836,22 +1836,22 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SP_PT_L shape Non Performing PT</t>
+          <t>SP_KT_L shape Non Performing Ex</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>85.06999999999999</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="E51" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F51" t="n">
-        <v>1202</v>
+        <v>1846</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1864,22 +1864,22 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>WB- SP- B0DB5VG39T - PT</t>
+          <t>SP_KT_L shape Non Performing Ex</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>266.98</v>
+        <v>93.08</v>
       </c>
       <c r="E52" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F52" t="n">
-        <v>1792</v>
+        <v>1669</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1892,22 +1892,22 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>WB- SP- B0DB5YTQZV-B0DB5VVPSB- PT</t>
+          <t>SP_PT_L shape Non Performing PT</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>341.36</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>985</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1920,22 +1920,22 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>WB- SP- B0DB5YTQZV-B0DB5VVPSB- PT</t>
+          <t>SP_PT_L shape Non Performing PT</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>224.55</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>2101</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1948,22 +1948,22 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>WB- SP- B0DP2VVRND - PT</t>
+          <t>WB- SP- B0DB5VG39T - PT</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>B0DP2VVRND</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>840.5600000000001</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>4683</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1976,22 +1976,22 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>WB- SP- B0DP2WC5VW - PT</t>
+          <t>WB- SP- B0DB5YTQZV-B0DB5VVPSB- PT</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>114.73</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -2004,22 +2004,22 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>WB- SP- B0DP32F346 - PT</t>
+          <t>WB- SP- B0DB5YTQZV-B0DB5VVPSB- PT</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>264.46</v>
+        <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>1727</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -2032,22 +2032,22 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>WB- SP-B0DB5W4TCP-PT</t>
+          <t>WB- SP- B0DP2VVRND - PT</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DP2VVRND</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>249.31</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>441</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -2060,22 +2060,22 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>WM- Adj Metal desk- B0DB5W4TCP-SP-KT-Phrase</t>
+          <t>WB- SP- B0DP2WC5VW - PT</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>369.41</v>
+        <v>175.15</v>
       </c>
       <c r="E59" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F59" t="n">
-        <v>1500</v>
+        <v>265</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -2088,22 +2088,22 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>WM- Height Adj stand Dual-B0DB5YTQZV-SP-KT-Phrase/BM</t>
+          <t>WB- SP- B0DP32F346 - PT</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>368.26</v>
+        <v>908.98</v>
       </c>
       <c r="E60" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="F60" t="n">
-        <v>2133</v>
+        <v>4025</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2116,35 +2116,35 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>WM- Height Adjustable stand- Dual-B0DB5YTQZV- PT</t>
+          <t>WB- SP-B0DB5W4TCP-PT</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>355.47</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>424</v>
+        <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>1093.22</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>WM- SP- Adj Metal desk- Multi Asins- PT</t>
+          <t>WM- Adj Metal desk- B0DB5W4TCP-SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2153,13 +2153,13 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>267.22</v>
+        <v>394.12</v>
       </c>
       <c r="E62" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F62" t="n">
-        <v>1144</v>
+        <v>2208</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2172,22 +2172,22 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>WM- SP- Height Adjustable stand- Dual-B0DB5YTQZV- Broad</t>
+          <t>WM- Height Adj stand - B0DP2VVRND-SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP2VVRND</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>215.14</v>
+        <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>1704</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2200,78 +2200,78 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>WM- SP- Wall Mounted Stand- B0DP2WC5VW- Broad</t>
+          <t>WM- Height Adj stand Dual-B0DB5YTQZV-SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>248.1</v>
+        <v>1330.13</v>
       </c>
       <c r="E64" t="n">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="F64" t="n">
-        <v>1505</v>
+        <v>7366</v>
       </c>
       <c r="G64" t="n">
-        <v>2795.76</v>
+        <v>3388.14</v>
       </c>
       <c r="H64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>WM- SP- Wooden Arm- B0DP32F346- PT</t>
+          <t>WM- Height Adjustable stand- Dual-B0DB5YTQZV- PT</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>369</v>
+        <v>1005.54</v>
       </c>
       <c r="E65" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F65" t="n">
-        <v>1850</v>
+        <v>1125</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>8295.76</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>WM- SP-Wall Mounted Stand- B0DP2WC5VW- Exact &amp; Phrase</t>
+          <t>WM- SP- Adj Metal desk- Multi Asins- PT</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>386.84</v>
+        <v>585.14</v>
       </c>
       <c r="E66" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F66" t="n">
-        <v>926</v>
+        <v>5025</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2284,106 +2284,106 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>WM- Wall Mounted Stand- B0DP2WC5VW- PT</t>
+          <t>WM- SP- Adj Metal desk- Multi Asins- PT</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>225.08</v>
+        <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>2795.76</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>WM- Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
+          <t>WM- SP- Height Adjustable stand- Dual-B0DB5YTQZV- Broad</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>678.88</v>
+        <v>460.3099999999999</v>
       </c>
       <c r="E68" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F68" t="n">
-        <v>2674</v>
+        <v>4749</v>
       </c>
       <c r="G68" t="n">
-        <v>5591.52</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>WM-Gas Spring MA- B0DB5VG39T-SP-KT-Phrase/BM</t>
+          <t>WM- SP- Wall Mounted Stand- B0DP2WC5VW- Broad</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>306.8</v>
+        <v>420.42</v>
       </c>
       <c r="E69" t="n">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="F69" t="n">
-        <v>1805</v>
+        <v>3300</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>2795.76</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
+          <t>WM- SP- Wooden Arm- B0DP32F346- PT</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>57.36</v>
+        <v>1137.1</v>
       </c>
       <c r="E70" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="F70" t="n">
-        <v>768</v>
+        <v>7602</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2396,7 +2396,7 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
+          <t>WM- SP-Wall Mounted Stand- B0DP2WC5VW- Exact &amp; Phrase</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2405,13 +2405,13 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>175.47</v>
+        <v>1007.43</v>
       </c>
       <c r="E71" t="n">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="F71" t="n">
-        <v>4132</v>
+        <v>2432</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2424,78 +2424,78 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
+          <t>WM- Wall Mounted Stand- B0DP2WC5VW- PT</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>38.17</v>
+        <v>765.0600000000001</v>
       </c>
       <c r="E72" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="F72" t="n">
-        <v>817</v>
+        <v>2086</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>8375.42</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
+          <t>WM- Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>89.43000000000001</v>
+        <v>1604.05</v>
       </c>
       <c r="E73" t="n">
-        <v>7</v>
+        <v>78</v>
       </c>
       <c r="F73" t="n">
-        <v>2143</v>
+        <v>8266</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>5591.52</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
+          <t>WM- Wall Mounted Stand- B0DP2WC5VW- SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>36.87</v>
+        <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>256</v>
+        <v>0</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2508,22 +2508,22 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
+          <t>WM-Gas Spring MA- B0DB5VG39T-SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>252.09</v>
+        <v>1168.4</v>
       </c>
       <c r="E75" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="F75" t="n">
-        <v>993</v>
+        <v>4368</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2536,22 +2536,22 @@
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
+          <t>WM-Gas Spring MA- Dual - B0DB5VVPSB-SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>38.81</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>358</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2564,22 +2564,22 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>25.78</v>
+        <v>480.22</v>
       </c>
       <c r="E77" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="F77" t="n">
-        <v>135</v>
+        <v>2829</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2592,7 +2592,7 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - exact</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2601,13 +2601,13 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>275.97</v>
+        <v>462.78</v>
       </c>
       <c r="E78" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F78" t="n">
-        <v>5855</v>
+        <v>12115</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2620,22 +2620,22 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>WM-SP- Premium Monitor Arms- Multi Asins -Phrase</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>B0DP3194QN</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
+        <v>308.73</v>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>2771</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2648,7 +2648,7 @@
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>WM-SP- Premium Monitor Arms- Multi Asins -Phrase</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2657,13 +2657,13 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>263.12</v>
+        <v>163.51</v>
       </c>
       <c r="E80" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F80" t="n">
-        <v>1726</v>
+        <v>5395</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2676,106 +2676,106 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring -Multi Asins- Phrase &amp; Exact</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>354.96</v>
+        <v>91.50999999999999</v>
       </c>
       <c r="E81" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F81" t="n">
-        <v>5896</v>
+        <v>783</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>1481.36</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring -Multi Asins- Phrase &amp; Exact</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>797.78</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>3714</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>2783.9</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T- Broad</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>336.2</v>
+        <v>319.74</v>
       </c>
       <c r="E83" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F83" t="n">
-        <v>5908</v>
+        <v>1247</v>
       </c>
       <c r="G83" t="n">
-        <v>4659.32</v>
+        <v>2372.03</v>
       </c>
       <c r="H83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T- Exact &amp; Phrase</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>51.32</v>
       </c>
       <c r="E84" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2788,22 +2788,22 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - exact</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>340.6</v>
+        <v>689.99</v>
       </c>
       <c r="E85" t="n">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="F85" t="n">
-        <v>537</v>
+        <v>15253</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2816,22 +2816,22 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
+          <t>WM-SP- Premium Monitor Arms- Multi Asins -Phrase</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DP3194QN</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>71.06999999999999</v>
+        <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>208</v>
+        <v>0</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2844,22 +2844,22 @@
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Branded</t>
+          <t>WM-SP- Premium Monitor Arms- Multi Asins -Phrase</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>30.2</v>
+        <v>1083.62</v>
       </c>
       <c r="E87" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="F87" t="n">
-        <v>293</v>
+        <v>9690</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2872,22 +2872,22 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Branded</t>
+          <t>WM-SP-Gas Spring -Multi Asins- Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>24</v>
+        <v>1259.62</v>
       </c>
       <c r="E88" t="n">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="F88" t="n">
-        <v>164</v>
+        <v>25058</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2900,22 +2900,22 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Branded</t>
+          <t>WM-SP-Gas Spring -Multi Asins- Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>16.17</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>375</v>
+        <v>0</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2928,50 +2928,50 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Branded</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T- Broad</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>18.09</v>
+        <v>1101.77</v>
       </c>
       <c r="E90" t="n">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="F90" t="n">
-        <v>199</v>
+        <v>13619</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>15025.44</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Branded</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T- Exact &amp; Phrase</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>74.61</v>
+        <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>823</v>
+        <v>0</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2984,50 +2984,50 @@
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Branded</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>855.2900000000001</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F92" t="n">
-        <v>677</v>
+        <v>1575</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>2329.66</v>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Defensive</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>14.54</v>
+        <v>172.21</v>
       </c>
       <c r="E93" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F93" t="n">
-        <v>154</v>
+        <v>730</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -3040,22 +3040,22 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Defensive</t>
+          <t>WM-SP-Monitor Arms- Branded</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>49.44</v>
+        <v>237.88</v>
       </c>
       <c r="E94" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F94" t="n">
-        <v>300</v>
+        <v>2347</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Defensive</t>
+          <t>WM-SP-Monitor Arms- Branded</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>9.69</v>
+        <v>39.28</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F95" t="n">
-        <v>134</v>
+        <v>525</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -3096,22 +3096,22 @@
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Defensive</t>
+          <t>WM-SP-Monitor Arms- Branded</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>58.46</v>
+        <v>57.46</v>
       </c>
       <c r="E96" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F96" t="n">
-        <v>849</v>
+        <v>1194</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -3124,22 +3124,22 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Defensive</t>
+          <t>WM-SP-Monitor Arms- Branded</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>14.54</v>
+        <v>28.09</v>
       </c>
       <c r="E97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F97" t="n">
-        <v>549</v>
+        <v>613</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -3152,50 +3152,50 @@
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Defensive</t>
+          <t>WM-SP-Monitor Arms- Branded</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>14.54</v>
+        <v>158.09</v>
       </c>
       <c r="E98" t="n">
+        <v>9</v>
+      </c>
+      <c r="F98" t="n">
+        <v>2289</v>
+      </c>
+      <c r="G98" t="n">
+        <v>7202.54</v>
+      </c>
+      <c r="H98" t="n">
         <v>1</v>
-      </c>
-      <c r="F98" t="n">
-        <v>102</v>
-      </c>
-      <c r="G98" t="n">
-        <v>0</v>
-      </c>
-      <c r="H98" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - PT</t>
+          <t>WM-SP-Monitor Arms- Branded</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>271.09</v>
+        <v>37.12</v>
       </c>
       <c r="E99" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F99" t="n">
-        <v>1048</v>
+        <v>2165</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3208,22 +3208,22 @@
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - Phrase</t>
+          <t>WM-SP-Monitor Arms- Defensive</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>265</v>
+        <v>78.87</v>
       </c>
       <c r="E100" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F100" t="n">
-        <v>695</v>
+        <v>527</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3236,22 +3236,22 @@
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 -Phrase</t>
+          <t>WM-SP-Monitor Arms- Defensive</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>261.69</v>
+        <v>107.6</v>
       </c>
       <c r="E101" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F101" t="n">
-        <v>2078</v>
+        <v>915</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3264,22 +3264,22 @@
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>WM-SP-POS stand- Multi - PT</t>
+          <t>WM-SP-Monitor Arms- Defensive</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>B0FN4FPJ83</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
+        <v>49.44</v>
       </c>
       <c r="E102" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F102" t="n">
-        <v>3</v>
+        <v>642</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3292,50 +3292,50 @@
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
+          <t>WM-SP-Monitor Arms- Defensive</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>B0FN4DSQ6P</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>144.83</v>
+        <v>203.4</v>
       </c>
       <c r="E103" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F103" t="n">
-        <v>638</v>
+        <v>2983</v>
       </c>
       <c r="G103" t="n">
-        <v>490.68</v>
+        <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
+          <t>WM-SP-Monitor Arms- Defensive</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>B0FN4HDM6Z</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>113.43</v>
+        <v>177.21</v>
       </c>
       <c r="E104" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F104" t="n">
-        <v>316</v>
+        <v>2344</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3348,106 +3348,106 @@
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
+          <t>WM-SP-Monitor Arms- Defensive</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>B0FHVWHQHR</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="E105" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F105" t="n">
-        <v>27</v>
+        <v>427</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>2626.27</v>
       </c>
       <c r="H105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
+          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - PT</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>B0FN4D3C89</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>155.71</v>
+        <v>572.24</v>
       </c>
       <c r="E106" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F106" t="n">
-        <v>2253</v>
+        <v>3151</v>
       </c>
       <c r="G106" t="n">
-        <v>617.8</v>
+        <v>4744.06</v>
       </c>
       <c r="H106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
+          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - Phrase</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>B0FN4DSQ6P</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>0</v>
+        <v>1081.85</v>
       </c>
       <c r="E107" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="F107" t="n">
-        <v>186</v>
+        <v>3489</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>2372.03</v>
       </c>
       <c r="H107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 -Phrase</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>B0FHVWHQHR</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0</v>
+        <v>1079.3</v>
       </c>
       <c r="E108" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="F108" t="n">
-        <v>69</v>
+        <v>10603</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3460,35 +3460,35 @@
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+          <t>WM-SP-POS stand- Multi - PT</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>B0FN4D3C89</t>
+          <t>B0FN4FPJ83</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>104.4</v>
+        <v>0</v>
       </c>
       <c r="E109" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>674</v>
+        <v>7</v>
       </c>
       <c r="G109" t="n">
-        <v>363.56</v>
+        <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3497,26 +3497,26 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>34.32</v>
+        <v>378.41</v>
       </c>
       <c r="E110" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F110" t="n">
-        <v>243</v>
+        <v>2229</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>490.68</v>
       </c>
       <c r="H110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3525,13 +3525,13 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>136.57</v>
+        <v>256.13</v>
       </c>
       <c r="E111" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F111" t="n">
-        <v>217</v>
+        <v>988</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3544,84 +3544,420 @@
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
+          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>B0FN4D3C89</t>
+          <t>B0FHVWHQHR</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>238.35</v>
+        <v>0</v>
       </c>
       <c r="E112" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>1652</v>
+        <v>197</v>
       </c>
       <c r="G112" t="n">
-        <v>1636.44</v>
+        <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
+          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>B0FN4DSQ6P</t>
+          <t>B0FN4D3C89</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>24.87</v>
+        <v>418.32</v>
       </c>
       <c r="E113" t="n">
+        <v>52</v>
+      </c>
+      <c r="F113" t="n">
+        <v>7182</v>
+      </c>
+      <c r="G113" t="n">
+        <v>1344.92</v>
+      </c>
+      <c r="H113" t="n">
         <v>3</v>
-      </c>
-      <c r="F113" t="n">
-        <v>416</v>
-      </c>
-      <c r="G113" t="n">
-        <v>617.8</v>
-      </c>
-      <c r="H113" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
+          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>B0FN4DSQ6P</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>40.51000000000001</v>
+      </c>
+      <c r="E114" t="n">
+        <v>6</v>
+      </c>
+      <c r="F114" t="n">
+        <v>1150</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>B0FHVWHQHR</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>14.67</v>
+      </c>
+      <c r="E115" t="n">
+        <v>1</v>
+      </c>
+      <c r="F115" t="n">
+        <v>599</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr"/>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>B0FN4D3C89</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>225.02</v>
+      </c>
+      <c r="E116" t="n">
+        <v>11</v>
+      </c>
+      <c r="F116" t="n">
+        <v>1703</v>
+      </c>
+      <c r="G116" t="n">
+        <v>363.56</v>
+      </c>
+      <c r="H116" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr"/>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>B0FN4DSQ6P</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>259.22</v>
+      </c>
+      <c r="E117" t="n">
+        <v>9</v>
+      </c>
+      <c r="F117" t="n">
+        <v>827</v>
+      </c>
+      <c r="G117" t="n">
+        <v>490.68</v>
+      </c>
+      <c r="H117" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr"/>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>B0FN4HDM6Z</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>401.09</v>
+      </c>
+      <c r="E118" t="n">
+        <v>17</v>
+      </c>
+      <c r="F118" t="n">
+        <v>457</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1778.81</v>
+      </c>
+      <c r="H118" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr"/>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>B0FN4D3C89</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>441.84</v>
+      </c>
+      <c r="E119" t="n">
+        <v>39</v>
+      </c>
+      <c r="F119" t="n">
+        <v>4751</v>
+      </c>
+      <c r="G119" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H119" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr"/>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>B0FN4DSQ6P</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>73.84999999999999</v>
+      </c>
+      <c r="E120" t="n">
+        <v>7</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1228</v>
+      </c>
+      <c r="G120" t="n">
+        <v>1599.16</v>
+      </c>
+      <c r="H120" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr"/>
+      <c r="B121" t="inlineStr">
+        <is>
           <t>WM_SP_KT_Adjustable_Exact_Manual_HV</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
+      <c r="C121" t="inlineStr">
         <is>
           <t>B0CPT3Q25C</t>
         </is>
       </c>
-      <c r="D114" t="n">
-        <v>515.35</v>
-      </c>
-      <c r="E114" t="n">
-        <v>21</v>
-      </c>
-      <c r="F114" t="n">
-        <v>8457</v>
-      </c>
-      <c r="G114" t="n">
+      <c r="D121" t="n">
+        <v>1473.79</v>
+      </c>
+      <c r="E121" t="n">
+        <v>58</v>
+      </c>
+      <c r="F121" t="n">
+        <v>29827</v>
+      </c>
+      <c r="G121" t="n">
         <v>12712.71</v>
       </c>
-      <c r="H114" t="n">
+      <c r="H121" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr"/>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>White Mulberry-Lshape-SP-KT-Phrase</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>B0BFVMDJ2K</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" t="n">
+        <v>32</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr"/>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>White Mulberry-Lshape-SP-KT-Phrase</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>B0BFW59TRG</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="E123" t="n">
+        <v>1</v>
+      </c>
+      <c r="F123" t="n">
+        <v>47</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr"/>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>White Mulberry-Motorized-SP-KT-BM</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>B0CPT3Q25C</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>171.29</v>
+      </c>
+      <c r="E124" t="n">
+        <v>13</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1408</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr"/>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>White Mulberry-Motorized-SP-KT-BM</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>B0DQ4YWSMC</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" t="n">
+        <v>214</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr"/>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>White-B0FN81FD8M-monitor arm (high price)-SP-KT-Phrase</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>B0FN81FD8M</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>26.26</v>
+      </c>
+      <c r="E126" t="n">
+        <v>2</v>
+      </c>
+      <c r="F126" t="n">
+        <v>383</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3917,13 +4253,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>123.09</v>
+        <v>213.94</v>
       </c>
       <c r="E10" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>3573</v>
+        <v>9607</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -3945,13 +4281,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>118.76</v>
+        <v>361.06</v>
       </c>
       <c r="E11" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="F11" t="n">
-        <v>5149</v>
+        <v>15188</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -4029,19 +4365,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>84.45999999999999</v>
+        <v>420.38</v>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="F14" t="n">
-        <v>2306</v>
+        <v>19468</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2783.9</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -4057,13 +4393,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>136.82</v>
+        <v>282.95</v>
       </c>
       <c r="E15" t="n">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F15" t="n">
-        <v>4776</v>
+        <v>11435</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -4167,7 +4503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4221,7 +4557,7 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Camb-SB-Defensive</t>
+          <t>Camb-SB-Branded-Phrase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -4230,13 +4566,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>286</v>
+        <v>20</v>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>72.09333333333333</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -4254,7 +4590,7 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Camb-SB-Defensive</t>
+          <t>Camb-SB-Branded-Phrase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -4263,13 +4599,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>286</v>
+        <v>20</v>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>72.09333333333333</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -4287,7 +4623,7 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Camb-SB-Defensive</t>
+          <t>Camb-SB-Branded-Phrase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -4296,13 +4632,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>286</v>
+        <v>20</v>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>72.09333333333333</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -4320,7 +4656,7 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Camb-SB-Defensive</t>
+          <t>Camb-SB-Branded-Phrase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4329,13 +4665,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>286</v>
+        <v>20</v>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>72.09333333333333</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -4353,7 +4689,7 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Camb-SB-Defensive</t>
+          <t>Camb-SB-Branded-Phrase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4362,13 +4698,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>286</v>
+        <v>20</v>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>72.09333333333333</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -4386,7 +4722,7 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Camb-SB-Defensive</t>
+          <t>Camb-SB-Branded-Phrase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4395,13 +4731,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>286</v>
+        <v>20</v>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>72.09333333333333</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -4419,7 +4755,7 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
+          <t>Camb-SB-Defensive</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4428,16 +4764,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1337</v>
+        <v>655</v>
       </c>
       <c r="E8" t="n">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="F8" t="n">
-        <v>124.715</v>
+        <v>139.0583333333333</v>
       </c>
       <c r="G8" t="n">
-        <v>3558.9</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -4452,25 +4788,25 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
+          <t>Camb-SB-Defensive</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVNS8HS</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1337</v>
+        <v>655</v>
       </c>
       <c r="E9" t="n">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="F9" t="n">
-        <v>124.715</v>
+        <v>139.0583333333333</v>
       </c>
       <c r="G9" t="n">
-        <v>3558.9</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4485,28 +4821,28 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
+          <t>Camb-SB-Defensive</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1846</v>
+        <v>655</v>
       </c>
       <c r="E10" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F10" t="n">
-        <v>249.82</v>
+        <v>139.0583333333333</v>
       </c>
       <c r="G10" t="n">
-        <v>19915.25</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -4518,28 +4854,28 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
+          <t>Camb-SB-Defensive</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1483</v>
+        <v>655</v>
       </c>
       <c r="E11" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F11" t="n">
-        <v>255.37</v>
+        <v>139.0583333333333</v>
       </c>
       <c r="G11" t="n">
-        <v>2626.27</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -4551,22 +4887,22 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
+          <t>Camb-SB-Defensive</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3376</v>
+        <v>655</v>
       </c>
       <c r="E12" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F12" t="n">
-        <v>350.84</v>
+        <v>139.0583333333333</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -4584,22 +4920,22 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Defensive</t>
+          <t>Camb-SB-Defensive</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>280</v>
+        <v>655</v>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F13" t="n">
-        <v>50.04166666666666</v>
+        <v>139.0583333333333</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -4617,28 +4953,28 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Defensive</t>
+          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>280</v>
+        <v>2914</v>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>120</v>
       </c>
       <c r="F14" t="n">
-        <v>50.04166666666666</v>
+        <v>273.555</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>10761.44</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -4650,28 +4986,28 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Defensive</t>
+          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>280</v>
+        <v>2914</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>120</v>
       </c>
       <c r="F15" t="n">
-        <v>50.04166666666666</v>
+        <v>273.555</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>10761.44</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -4683,28 +5019,28 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Defensive</t>
+          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>280</v>
+        <v>1822</v>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="F16" t="n">
-        <v>50.04166666666666</v>
+        <v>248.82</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>6638.416666666667</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -4716,28 +5052,28 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Defensive</t>
+          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DQ1NV8D2</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>280</v>
+        <v>1822</v>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="F17" t="n">
-        <v>50.04166666666666</v>
+        <v>248.82</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>6638.416666666667</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -4749,28 +5085,28 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Defensive</t>
+          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>280</v>
+        <v>1822</v>
       </c>
       <c r="E18" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="F18" t="n">
-        <v>50.04166666666666</v>
+        <v>248.82</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>6638.416666666667</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -4782,30 +5118,492 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
+          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>4554</v>
+      </c>
+      <c r="E19" t="n">
+        <v>54</v>
+      </c>
+      <c r="F19" t="n">
+        <v>637.09</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2626.27</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>B0DP2WC5VW</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>9474</v>
+      </c>
+      <c r="E20" t="n">
+        <v>92</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1295.72</v>
+      </c>
+      <c r="G20" t="n">
+        <v>5579.66</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>B0DB5VVPSB</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>B0DB5W4TCP</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>B0DB5YTQZV</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>B0DP2Z5DQ9</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Defensive</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>634</v>
+      </c>
+      <c r="E27" t="n">
+        <v>10</v>
+      </c>
+      <c r="F27" t="n">
+        <v>102.1883333333333</v>
+      </c>
+      <c r="G27" t="n">
+        <v>388.2766666666666</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Defensive</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>B0DB5VVPSB</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>634</v>
+      </c>
+      <c r="E28" t="n">
+        <v>10</v>
+      </c>
+      <c r="F28" t="n">
+        <v>102.1883333333333</v>
+      </c>
+      <c r="G28" t="n">
+        <v>388.2766666666666</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Defensive</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>B0DB5W4TCP</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>634</v>
+      </c>
+      <c r="E29" t="n">
+        <v>10</v>
+      </c>
+      <c r="F29" t="n">
+        <v>102.1883333333333</v>
+      </c>
+      <c r="G29" t="n">
+        <v>388.2766666666666</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Defensive</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>B0DB5YTQZV</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>634</v>
+      </c>
+      <c r="E30" t="n">
+        <v>10</v>
+      </c>
+      <c r="F30" t="n">
+        <v>102.1883333333333</v>
+      </c>
+      <c r="G30" t="n">
+        <v>388.2766666666666</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Defensive</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>B0DP2Z5DQ9</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>634</v>
+      </c>
+      <c r="E31" t="n">
+        <v>10</v>
+      </c>
+      <c r="F31" t="n">
+        <v>102.1883333333333</v>
+      </c>
+      <c r="G31" t="n">
+        <v>388.2766666666666</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Defensive</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>634</v>
+      </c>
+      <c r="E32" t="n">
+        <v>10</v>
+      </c>
+      <c r="F32" t="n">
+        <v>102.1883333333333</v>
+      </c>
+      <c r="G32" t="n">
+        <v>388.2766666666666</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>B0DB5VG39T</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v>2447</v>
-      </c>
-      <c r="E19" t="n">
-        <v>16</v>
-      </c>
-      <c r="F19" t="n">
-        <v>237.99</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="inlineStr">
+      <c r="D33" t="n">
+        <v>7908</v>
+      </c>
+      <c r="E33" t="n">
+        <v>55</v>
+      </c>
+      <c r="F33" t="n">
+        <v>950.28</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="inlineStr">
         <is>
           <t>White Mulberry</t>
         </is>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week23.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week23.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H126"/>
+  <dimension ref="A1:H135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -641,13 +641,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1204.02</v>
+        <v>1556.51</v>
       </c>
       <c r="E8" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="F8" t="n">
-        <v>10841</v>
+        <v>13616</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>976.74</v>
+        <v>2003.88</v>
       </c>
       <c r="E9" t="n">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="F9" t="n">
-        <v>9974</v>
+        <v>20565</v>
       </c>
       <c r="G9" t="n">
         <v>7117.8</v>
@@ -697,13 +697,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>854.92</v>
+        <v>1816.54</v>
       </c>
       <c r="E10" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="F10" t="n">
-        <v>1494</v>
+        <v>3932</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -731,7 +731,7 @@
         <v>29</v>
       </c>
       <c r="F11" t="n">
-        <v>3950</v>
+        <v>3935</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>16</v>
       </c>
       <c r="F12" t="n">
-        <v>6069</v>
+        <v>6045</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
         <v>48</v>
       </c>
       <c r="F13" t="n">
-        <v>8449</v>
+        <v>8425</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -815,7 +815,7 @@
         <v>13</v>
       </c>
       <c r="F14" t="n">
-        <v>7321</v>
+        <v>7221</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -837,13 +837,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>310.19</v>
+        <v>796.27</v>
       </c>
       <c r="E15" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F15" t="n">
-        <v>870</v>
+        <v>2198</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -865,13 +865,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>276.2</v>
+        <v>570.41</v>
       </c>
       <c r="E16" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F16" t="n">
-        <v>1347</v>
+        <v>3235</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>812.5799999999999</v>
+        <v>1037.09</v>
       </c>
       <c r="E17" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="F17" t="n">
-        <v>10276</v>
+        <v>11353</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -921,13 +921,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>283.15</v>
+        <v>383.01</v>
       </c>
       <c r="E18" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F18" t="n">
-        <v>7295</v>
+        <v>9135</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -940,22 +940,22 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Camb-SP- L Shaped-B0BFWD6SNF-Exact &amp; Phrase(2)</t>
+          <t>Camb-Lshape-SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.53</v>
+        <v>860.53</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="F19" t="n">
-        <v>247</v>
+        <v>10109</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -968,22 +968,22 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Camb-SP-B0BFVNS8HS -L-Shape-Exact-phrase</t>
+          <t>Camb-Lshape-SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0BFVNS8HS</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>150.3</v>
+        <v>258.92</v>
       </c>
       <c r="E20" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F20" t="n">
-        <v>2429</v>
+        <v>6737</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -996,7 +996,7 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Camb-SP-Branded</t>
+          <t>Camb-Lshape-SP-PT-Exact</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1005,13 +1005,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>93.41</v>
+        <v>340.7</v>
       </c>
       <c r="E21" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F21" t="n">
-        <v>459</v>
+        <v>1785</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1024,22 +1024,22 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Camb-SP-Branded</t>
+          <t>Camb-Lshape-SP-PT-Exact</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0BFVNS8HS</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>374.57</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F22" t="n">
-        <v>2101</v>
+        <v>3361</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1052,22 +1052,22 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Camb-SP-Branded</t>
+          <t>Camb-Motorized-SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>17.09</v>
+        <v>175.77</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F23" t="n">
-        <v>291</v>
+        <v>1916</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1080,22 +1080,22 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Camb-SP-Branded</t>
+          <t>Camb-Motorized-SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>125.16</v>
+        <v>553.9200000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F24" t="n">
-        <v>687</v>
+        <v>18298</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1108,7 +1108,7 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Camb-SP-Branded</t>
+          <t>Camb-Motorized-SP-PT-Exact</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1117,26 +1117,26 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>289.13</v>
+        <v>684.59</v>
       </c>
       <c r="E25" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F25" t="n">
-        <v>1553</v>
+        <v>3503</v>
       </c>
       <c r="G25" t="n">
-        <v>11016.1</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Camb-SP-Branded</t>
+          <t>Camb-Motorized-SP-PT-Exact</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1145,13 +1145,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>104.2</v>
+        <v>142.62</v>
       </c>
       <c r="E26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F26" t="n">
-        <v>779</v>
+        <v>1161</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1164,22 +1164,22 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-B0BFVMDJ2K/B0BFWD6SNF- Exact/Phrase</t>
+          <t>Camb-SP- L Shaped-B0BFWD6SNF-Exact &amp; Phrase(2)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1565.55</v>
+        <v>39.07</v>
       </c>
       <c r="E27" t="n">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="F27" t="n">
-        <v>11853</v>
+        <v>596</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1192,50 +1192,50 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-B0BFWD6SNF - Broad</t>
+          <t>Camb-SP-B0BFVNS8HS -L-Shape-Exact-phrase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVNS8HS</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>510.59</v>
+        <v>312.17</v>
       </c>
       <c r="E28" t="n">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="F28" t="n">
-        <v>6835</v>
+        <v>7609</v>
       </c>
       <c r="G28" t="n">
-        <v>28428.8</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-CDesk-Multiple Asin- PT</t>
+          <t>Camb-SP-Branded</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>399.75</v>
+        <v>400.03</v>
       </c>
       <c r="E29" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F29" t="n">
-        <v>2631</v>
+        <v>1991</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1248,22 +1248,22 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multi Asin- AT</t>
+          <t>Camb-SP-Branded</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFVNS8HS</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>263.02</v>
+        <v>27.58</v>
       </c>
       <c r="E30" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>960</v>
+        <v>2659</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1276,22 +1276,22 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multi Asin- AT</t>
+          <t>Camb-SP-Branded</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B0BFVNS8HS</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>125.11</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F31" t="n">
-        <v>40</v>
+        <v>1518</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1304,22 +1304,22 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multi Asin- AT</t>
+          <t>Camb-SP-Branded</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>89.8</v>
+        <v>487.19</v>
       </c>
       <c r="E32" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="F32" t="n">
-        <v>1095</v>
+        <v>6347</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1332,50 +1332,50 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multi Asin- AT</t>
+          <t>Camb-SP-Branded</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>93.31999999999999</v>
+        <v>852.89</v>
       </c>
       <c r="E33" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="F33" t="n">
-        <v>1171</v>
+        <v>6394</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>22032.2</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multiple Asins- Exact 01</t>
+          <t>Camb-SP-Branded</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1382.91</v>
+        <v>124.91</v>
       </c>
       <c r="E34" t="n">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="F34" t="n">
-        <v>19479</v>
+        <v>1493</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1388,22 +1388,22 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multiple Asins- Exact 01</t>
+          <t>Camb-SP-Lshape-B0BFVMDJ2K/B0BFWD6SNF- Exact/Phrase</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>335.05</v>
+        <v>3389.71</v>
       </c>
       <c r="E35" t="n">
-        <v>14</v>
+        <v>146</v>
       </c>
       <c r="F35" t="n">
-        <v>4353</v>
+        <v>25286</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1416,35 +1416,35 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multiple Asins- Exact/Phrase</t>
+          <t>Camb-SP-Lshape-B0BFWD6SNF - Broad</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>150.65</v>
+        <v>1052.21</v>
       </c>
       <c r="E36" t="n">
-        <v>10</v>
+        <v>115</v>
       </c>
       <c r="F36" t="n">
-        <v>1371</v>
+        <v>12849</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>49782.18</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multiple Asins- Exact/Phrase</t>
+          <t>Camb-SP-Lshape-CDesk-Multiple Asin- PT</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1453,41 +1453,41 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1039.42</v>
+        <v>1298.48</v>
       </c>
       <c r="E37" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F37" t="n">
-        <v>18340</v>
+        <v>5566</v>
       </c>
       <c r="G37" t="n">
-        <v>7075.42</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multiple Asins- Exact/Phrase</t>
+          <t>Camb-SP-Lshape-Multi Asin- AT</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>198.65</v>
+        <v>263.02</v>
       </c>
       <c r="E38" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F38" t="n">
-        <v>2984</v>
+        <v>960</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1500,22 +1500,22 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Camb-SP-Motorized Desk- B0CPT3Q25C- Exact</t>
+          <t>Camb-SP-Lshape-Multi Asin- AT</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0BFVNS8HS</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1036.11</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>8976</v>
+        <v>40</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1528,22 +1528,22 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Camb-SP-Motorized Desk-B0CPT3Q25C - PT01</t>
+          <t>Camb-SP-Lshape-Multi Asin- AT</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>971.0700000000001</v>
+        <v>89.8</v>
       </c>
       <c r="E40" t="n">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="F40" t="n">
-        <v>5559</v>
+        <v>1095</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1556,22 +1556,22 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Camb-SP-Motorized Desk-B0CPT3Q25C- Exact</t>
+          <t>Camb-SP-Lshape-Multi Asin- AT</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1717.93</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="F41" t="n">
-        <v>16289</v>
+        <v>1171</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1584,50 +1584,50 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Camb-SP-Zshape-B0CPFS24ML- CT ref</t>
+          <t>Camb-SP-Lshape-Multiple Asins- Exact 01</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1127.24</v>
+        <v>3157.18</v>
       </c>
       <c r="E42" t="n">
-        <v>64</v>
+        <v>149</v>
       </c>
       <c r="F42" t="n">
-        <v>5609</v>
+        <v>40736</v>
       </c>
       <c r="G42" t="n">
-        <v>7202.54</v>
+        <v>13105.08</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Camb-SP-Zshape-B0CPFS24ML- PT</t>
+          <t>Camb-SP-Lshape-Multiple Asins- Exact 01</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1329.11</v>
+        <v>462.51</v>
       </c>
       <c r="E43" t="n">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="F43" t="n">
-        <v>6387</v>
+        <v>6918</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1640,22 +1640,22 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Camb-SP-Zshape-B0CPFS24ML- Phrase</t>
+          <t>Camb-SP-Lshape-Multiple Asins- Exact/Phrase</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1133.71</v>
+        <v>358.74</v>
       </c>
       <c r="E44" t="n">
-        <v>95</v>
+        <v>21</v>
       </c>
       <c r="F44" t="n">
-        <v>13216</v>
+        <v>3551</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1668,50 +1668,50 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Camb-SP-Zshape-B0CPFS24ML-PT01</t>
+          <t>Camb-SP-Lshape-Multiple Asins- Exact/Phrase</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>595.46</v>
+        <v>2471.67</v>
       </c>
       <c r="E45" t="n">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="F45" t="n">
-        <v>2450</v>
+        <v>35503</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>7075.42</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Camb-SP-stand desk- B0DQ1NV8D2- PT</t>
+          <t>Camb-SP-Lshape-Multiple Asins- Exact/Phrase</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>827.4299999999999</v>
+        <v>505.04</v>
       </c>
       <c r="E46" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F46" t="n">
-        <v>3145</v>
+        <v>8532</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1724,78 +1724,78 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Camb-Zshape-Gaming- B0CPFS24ML-Phrase/Exact</t>
+          <t>Camb-SP-Motorized Desk- B0CPT3Q25C- Exact</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1655.8</v>
+        <v>1036.11</v>
       </c>
       <c r="E47" t="n">
-        <v>161</v>
+        <v>27</v>
       </c>
       <c r="F47" t="n">
-        <v>22289</v>
+        <v>8965</v>
       </c>
       <c r="G47" t="n">
-        <v>7202.54</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SP CT PT_B0CPFS24ML_Gaming</t>
+          <t>Camb-SP-Motorized Desk-B0CPT3Q25C - PT01</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1037.06</v>
+        <v>2398.7</v>
       </c>
       <c r="E48" t="n">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="F48" t="n">
-        <v>9445</v>
+        <v>12424</v>
       </c>
       <c r="G48" t="n">
-        <v>14405.08</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SP KT_B0CPFS24ML_Manual_Gaming</t>
+          <t>Camb-SP-Motorized Desk-B0CPT3Q25C- Exact</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1178.62</v>
+        <v>1717.93</v>
       </c>
       <c r="E49" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F49" t="n">
-        <v>5927</v>
+        <v>16286</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1808,50 +1808,50 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SP_KT_L shape Non Performing Ex</t>
+          <t>Camb-SP-Zshape-B0CPFS24ML- CT ref</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>33.18</v>
+        <v>2632.43</v>
       </c>
       <c r="E50" t="n">
-        <v>2</v>
+        <v>147</v>
       </c>
       <c r="F50" t="n">
-        <v>1286</v>
+        <v>21973</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>21607.62</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SP_KT_L shape Non Performing Ex</t>
+          <t>Camb-SP-Zshape-B0CPFS24ML- PT</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>68.56999999999999</v>
+        <v>3018.27</v>
       </c>
       <c r="E51" t="n">
-        <v>3</v>
+        <v>198</v>
       </c>
       <c r="F51" t="n">
-        <v>1846</v>
+        <v>14498</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1864,78 +1864,78 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SP_KT_L shape Non Performing Ex</t>
+          <t>Camb-SP-Zshape-B0CPFS24ML- Phrase</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>93.08</v>
+        <v>2747.24</v>
       </c>
       <c r="E52" t="n">
-        <v>5</v>
+        <v>218</v>
       </c>
       <c r="F52" t="n">
-        <v>1669</v>
+        <v>30514</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>7202.54</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SP_PT_L shape Non Performing PT</t>
+          <t>Camb-SP-Zshape-B0CPFS24ML-PT01</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>341.36</v>
+        <v>1867.73</v>
       </c>
       <c r="E53" t="n">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="F53" t="n">
-        <v>985</v>
+        <v>6225</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>11016.1</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SP_PT_L shape Non Performing PT</t>
+          <t>Camb-SP-stand desk- B0DQ1NV8D2- PT</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>224.55</v>
+        <v>1826.2</v>
       </c>
       <c r="E54" t="n">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="F54" t="n">
-        <v>2101</v>
+        <v>6032</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1948,78 +1948,78 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>WB- SP- B0DB5VG39T - PT</t>
+          <t>Camb-Zshape-Gaming- B0CPFS24ML-Phrase/Exact</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>840.5600000000001</v>
+        <v>3603.81</v>
       </c>
       <c r="E55" t="n">
-        <v>44</v>
+        <v>347</v>
       </c>
       <c r="F55" t="n">
-        <v>4683</v>
+        <v>45883</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>14405.08</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>WB- SP- B0DB5YTQZV-B0DB5VVPSB- PT</t>
+          <t>SP CT PT_B0CPFS24ML_Gaming</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>2526.64</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>246</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>19145</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>14405.08</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>WB- SP- B0DB5YTQZV-B0DB5VVPSB- PT</t>
+          <t>SP KT_B0CPFS24ML_Manual_Gaming</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>1154.3</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>5915</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -2032,22 +2032,22 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>WB- SP- B0DP2VVRND - PT</t>
+          <t>SP_KT_L shape Non Performing Ex</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>B0DP2VVRND</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>249.31</v>
+        <v>185.02</v>
       </c>
       <c r="E58" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F58" t="n">
-        <v>441</v>
+        <v>2635</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -2060,22 +2060,22 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>WB- SP- B0DP2WC5VW - PT</t>
+          <t>SP_KT_L shape Non Performing Ex</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>175.15</v>
+        <v>231.9</v>
       </c>
       <c r="E59" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F59" t="n">
-        <v>265</v>
+        <v>3142</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -2088,22 +2088,22 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>WB- SP- B0DP32F346 - PT</t>
+          <t>SP_KT_L shape Non Performing Ex</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>908.98</v>
+        <v>228.14</v>
       </c>
       <c r="E60" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="F60" t="n">
-        <v>4025</v>
+        <v>4240</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2116,22 +2116,22 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>WB- SP-B0DB5W4TCP-PT</t>
+          <t>SP_PT_L shape Non Performing PT</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>993.91</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>3099</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2144,22 +2144,22 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>WM- Adj Metal desk- B0DB5W4TCP-SP-KT-Phrase</t>
+          <t>SP_PT_L shape Non Performing PT</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>394.12</v>
+        <v>841.9100000000001</v>
       </c>
       <c r="E62" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="F62" t="n">
-        <v>2208</v>
+        <v>6758</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2172,22 +2172,22 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>WM- Height Adj stand - B0DP2VVRND-SP-KT-Phrase</t>
+          <t>WB- SP- B0DB5VG39T - PT</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>B0DP2VVRND</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>1811.25</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>10841</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2200,35 +2200,35 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>WM- Height Adj stand Dual-B0DB5YTQZV-SP-KT-Phrase/BM</t>
+          <t>WB- SP- B0DB5YTQZV-B0DB5VVPSB- PT</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1330.13</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>7366</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>3388.14</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>WM- Height Adjustable stand- Dual-B0DB5YTQZV- PT</t>
+          <t>WB- SP- B0DB5YTQZV-B0DB5VVPSB- PT</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2237,41 +2237,41 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1005.54</v>
+        <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>1125</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>8295.76</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>WM- SP- Adj Metal desk- Multi Asins- PT</t>
+          <t>WB- SP- B0DP2VVRND - PT</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DP2VVRND</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>585.14</v>
+        <v>249.31</v>
       </c>
       <c r="E66" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F66" t="n">
-        <v>5025</v>
+        <v>440</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2284,22 +2284,22 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>WM- SP- Adj Metal desk- Multi Asins- PT</t>
+          <t>WB- SP- B0DP2WC5VW - PT</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>175.15</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>264</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2312,78 +2312,78 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>WM- SP- Height Adjustable stand- Dual-B0DB5YTQZV- Broad</t>
+          <t>WB- SP- B0DP32F346 - PT</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>460.3099999999999</v>
+        <v>2040.75</v>
       </c>
       <c r="E68" t="n">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="F68" t="n">
-        <v>4749</v>
+        <v>6587</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>2626.27</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>WM- SP- Wall Mounted Stand- B0DP2WC5VW- Broad</t>
+          <t>WB- SP-B0DB5W4TCP-PT</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>420.42</v>
+        <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>3300</v>
+        <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>2795.76</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>WM- SP- Wooden Arm- B0DP32F346- PT</t>
+          <t>WM- Adj Metal desk- B0DB5W4TCP-SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1137.1</v>
+        <v>394.12</v>
       </c>
       <c r="E70" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="F70" t="n">
-        <v>7602</v>
+        <v>2208</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2396,22 +2396,22 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>WM- SP-Wall Mounted Stand- B0DP2WC5VW- Exact &amp; Phrase</t>
+          <t>WM- Height Adj stand - B0DP2VVRND-SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DP2VVRND</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1007.43</v>
+        <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>2432</v>
+        <v>0</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2424,78 +2424,78 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>WM- Wall Mounted Stand- B0DP2WC5VW- PT</t>
+          <t>WM- Height Adj stand Dual-B0DB5YTQZV-SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>765.0600000000001</v>
+        <v>3059.83</v>
       </c>
       <c r="E72" t="n">
-        <v>44</v>
+        <v>139</v>
       </c>
       <c r="F72" t="n">
-        <v>2086</v>
+        <v>19932</v>
       </c>
       <c r="G72" t="n">
-        <v>8375.42</v>
+        <v>3388.14</v>
       </c>
       <c r="H72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>WM- Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
+          <t>WM- Height Adjustable stand- Dual-B0DB5YTQZV- PT</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1604.05</v>
+        <v>2202.9</v>
       </c>
       <c r="E73" t="n">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F73" t="n">
-        <v>8266</v>
+        <v>3251</v>
       </c>
       <c r="G73" t="n">
-        <v>5591.52</v>
+        <v>10829.66</v>
       </c>
       <c r="H73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>WM- Wall Mounted Stand- B0DP2WC5VW- SP-KT-Phrase/BM</t>
+          <t>WM- SP- Adj Metal desk- Multi Asins- PT</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
+        <v>1021.35</v>
       </c>
       <c r="E74" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>7617</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2508,22 +2508,22 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>WM-Gas Spring MA- B0DB5VG39T-SP-KT-Phrase/BM</t>
+          <t>WM- SP- Adj Metal desk- Multi Asins- PT</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1168.4</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>4368</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2536,22 +2536,22 @@
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>WM-Gas Spring MA- Dual - B0DB5VVPSB-SP-KT-Phrase/BM</t>
+          <t>WM- SP- Height Adjustable stand- Dual-B0DB5YTQZV- Broad</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>941.77</v>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>11634</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2564,78 +2564,78 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
+          <t>WM- SP- Wall Mounted Stand- B0DP2WC5VW- Broad</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>480.22</v>
+        <v>444.67</v>
       </c>
       <c r="E77" t="n">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="F77" t="n">
-        <v>2829</v>
+        <v>3484</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>2795.76</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
+          <t>WM- SP- Wooden Arm- B0DP32F346- PT</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>462.78</v>
+        <v>2608.73</v>
       </c>
       <c r="E78" t="n">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="F78" t="n">
-        <v>12115</v>
+        <v>16332</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>12934.37</v>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
+          <t>WM- SP-Wall Mounted Stand- B0DP2WC5VW- Exact &amp; Phrase</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>308.73</v>
+        <v>1156.38</v>
       </c>
       <c r="E79" t="n">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="F79" t="n">
-        <v>2771</v>
+        <v>2912</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2648,63 +2648,63 @@
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
+          <t>WM- Wall Mounted Stand- B0DP2WC5VW- PT</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>163.51</v>
+        <v>859.1600000000001</v>
       </c>
       <c r="E80" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="F80" t="n">
-        <v>5395</v>
+        <v>2540</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>8375.42</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
+          <t>WM- Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>91.50999999999999</v>
+        <v>1959.49</v>
       </c>
       <c r="E81" t="n">
-        <v>5</v>
+        <v>93</v>
       </c>
       <c r="F81" t="n">
-        <v>783</v>
+        <v>10655</v>
       </c>
       <c r="G81" t="n">
-        <v>1481.36</v>
+        <v>8375.42</v>
       </c>
       <c r="H81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
+          <t>WM- Wall Mounted Stand- B0DP2WC5VW- SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2713,44 +2713,44 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>797.78</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>3714</v>
+        <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>2783.9</v>
+        <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
+          <t>WM-Gas Spring MA- B0DB5VG39T-SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>319.74</v>
+        <v>2534.24</v>
       </c>
       <c r="E83" t="n">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="F83" t="n">
-        <v>1247</v>
+        <v>11393</v>
       </c>
       <c r="G83" t="n">
-        <v>2372.03</v>
+        <v>2329.66</v>
       </c>
       <c r="H83" t="n">
         <v>1</v>
@@ -2760,22 +2760,22 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
+          <t>WM-Gas Spring MA- Dual - B0DB5VVPSB-SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>51.32</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2788,22 +2788,22 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - exact</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>689.99</v>
+        <v>1135.44</v>
       </c>
       <c r="E85" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="F85" t="n">
-        <v>15253</v>
+        <v>7834</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2816,50 +2816,50 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>WM-SP- Premium Monitor Arms- Multi Asins -Phrase</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>B0DP3194QN</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>565.67</v>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>12969</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>2965.25</v>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>WM-SP- Premium Monitor Arms- Multi Asins -Phrase</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1083.62</v>
+        <v>653.38</v>
       </c>
       <c r="E87" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="F87" t="n">
-        <v>9690</v>
+        <v>16094</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2872,22 +2872,22 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring -Multi Asins- Phrase &amp; Exact</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1259.62</v>
+        <v>534.4300000000001</v>
       </c>
       <c r="E88" t="n">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="F88" t="n">
-        <v>25058</v>
+        <v>19329</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2900,134 +2900,134 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring -Multi Asins- Phrase &amp; Exact</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>517.61</v>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>4120</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>2932.2</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T- Broad</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1101.77</v>
+        <v>1014.82</v>
       </c>
       <c r="E90" t="n">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="F90" t="n">
-        <v>13619</v>
+        <v>5140</v>
       </c>
       <c r="G90" t="n">
-        <v>15025.44</v>
+        <v>2783.9</v>
       </c>
       <c r="H90" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T- Exact &amp; Phrase</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>1102.53</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>7319</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>5155.93</v>
       </c>
       <c r="H91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>855.2900000000001</v>
+        <v>229.8</v>
       </c>
       <c r="E92" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F92" t="n">
-        <v>1575</v>
+        <v>2225</v>
       </c>
       <c r="G92" t="n">
-        <v>2329.66</v>
+        <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - exact</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>172.21</v>
+        <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>730</v>
+        <v>0</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -3040,22 +3040,22 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Branded</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - exact</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>237.88</v>
+        <v>859.26</v>
       </c>
       <c r="E94" t="n">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="F94" t="n">
-        <v>2347</v>
+        <v>17573</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Branded</t>
+          <t>WM-SP- Premium Monitor Arms- Multi Asins -Phrase</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DP3194QN</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>39.28</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>525</v>
+        <v>0</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -3096,22 +3096,22 @@
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Branded</t>
+          <t>WM-SP- Premium Monitor Arms- Multi Asins -Phrase</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>57.46</v>
+        <v>2452.04</v>
       </c>
       <c r="E96" t="n">
-        <v>3</v>
+        <v>96</v>
       </c>
       <c r="F96" t="n">
-        <v>1194</v>
+        <v>22496</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -3124,22 +3124,22 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Branded</t>
+          <t>WM-SP-Gas Spring -Multi Asins- Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>28.09</v>
+        <v>2528.17</v>
       </c>
       <c r="E97" t="n">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="F97" t="n">
-        <v>613</v>
+        <v>51448</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -3152,63 +3152,63 @@
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Branded</t>
+          <t>WM-SP-Gas Spring -Multi Asins- Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>158.09</v>
+        <v>0</v>
       </c>
       <c r="E98" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>2289</v>
+        <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>7202.54</v>
+        <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Branded</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T- Broad</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>37.12</v>
+        <v>2147.19</v>
       </c>
       <c r="E99" t="n">
-        <v>2</v>
+        <v>146</v>
       </c>
       <c r="F99" t="n">
-        <v>2165</v>
+        <v>26346</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>15025.44</v>
       </c>
       <c r="H99" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Defensive</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T- Exact &amp; Phrase</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3217,13 +3217,13 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>78.87</v>
+        <v>0</v>
       </c>
       <c r="E100" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>527</v>
+        <v>0</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3236,203 +3236,203 @@
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Defensive</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>107.6</v>
+        <v>1556.37</v>
       </c>
       <c r="E101" t="n">
-        <v>8</v>
+        <v>53</v>
       </c>
       <c r="F101" t="n">
-        <v>915</v>
+        <v>2409</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>6141.52</v>
       </c>
       <c r="H101" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Defensive</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>49.44</v>
+        <v>852.29</v>
       </c>
       <c r="E102" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F102" t="n">
-        <v>642</v>
+        <v>2473</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>4151.69</v>
       </c>
       <c r="H102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Defensive</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>203.4</v>
+        <v>134.76</v>
       </c>
       <c r="E103" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F103" t="n">
-        <v>2983</v>
+        <v>691</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>2372.03</v>
       </c>
       <c r="H103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Defensive</t>
+          <t>WM-SP-Monitor Arms- Branded</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>177.21</v>
+        <v>586.49</v>
       </c>
       <c r="E104" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="F104" t="n">
-        <v>2344</v>
+        <v>7351</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>2329.66</v>
       </c>
       <c r="H104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Defensive</t>
+          <t>WM-SP-Monitor Arms- Branded</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>65</v>
+        <v>176.9</v>
       </c>
       <c r="E105" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F105" t="n">
-        <v>427</v>
+        <v>1660</v>
       </c>
       <c r="G105" t="n">
-        <v>2626.27</v>
+        <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - PT</t>
+          <t>WM-SP-Monitor Arms- Branded</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>572.24</v>
+        <v>206.6</v>
       </c>
       <c r="E106" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="F106" t="n">
-        <v>3151</v>
+        <v>2753</v>
       </c>
       <c r="G106" t="n">
-        <v>4744.06</v>
+        <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - Phrase</t>
+          <t>WM-SP-Monitor Arms- Branded</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1081.85</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="E107" t="n">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="F107" t="n">
-        <v>3489</v>
+        <v>1936</v>
       </c>
       <c r="G107" t="n">
-        <v>2372.03</v>
+        <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 -Phrase</t>
+          <t>WM-SP-Monitor Arms- Branded</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3441,97 +3441,97 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1079.3</v>
+        <v>254.5</v>
       </c>
       <c r="E108" t="n">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="F108" t="n">
-        <v>10603</v>
+        <v>5165</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>7202.54</v>
       </c>
       <c r="H108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>WM-SP-POS stand- Multi - PT</t>
+          <t>WM-SP-Monitor Arms- Branded</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>B0FN4FPJ83</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0</v>
+        <v>173.56</v>
       </c>
       <c r="E109" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F109" t="n">
-        <v>7</v>
+        <v>4433</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>7944.92</v>
       </c>
       <c r="H109" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
+          <t>WM-SP-Monitor Arms- Defensive</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>B0FN4DSQ6P</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>378.41</v>
+        <v>161.18</v>
       </c>
       <c r="E110" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F110" t="n">
-        <v>2229</v>
+        <v>1131</v>
       </c>
       <c r="G110" t="n">
-        <v>490.68</v>
+        <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
+          <t>WM-SP-Monitor Arms- Defensive</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>B0FN4HDM6Z</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>256.13</v>
+        <v>257.39</v>
       </c>
       <c r="E111" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F111" t="n">
-        <v>988</v>
+        <v>3064</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3544,22 +3544,22 @@
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
+          <t>WM-SP-Monitor Arms- Defensive</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>B0FHVWHQHR</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0</v>
+        <v>135.68</v>
       </c>
       <c r="E112" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F112" t="n">
-        <v>197</v>
+        <v>1240</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3572,165 +3572,165 @@
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
+          <t>WM-SP-Monitor Arms- Defensive</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>B0FN4D3C89</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>418.32</v>
+        <v>469.36</v>
       </c>
       <c r="E113" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="F113" t="n">
-        <v>7182</v>
+        <v>5669</v>
       </c>
       <c r="G113" t="n">
-        <v>1344.92</v>
+        <v>1694.07</v>
       </c>
       <c r="H113" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
+          <t>WM-SP-Monitor Arms- Defensive</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>B0FN4DSQ6P</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>40.51000000000001</v>
+        <v>517.54</v>
       </c>
       <c r="E114" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="F114" t="n">
-        <v>1150</v>
+        <v>5793</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>4744.07</v>
       </c>
       <c r="H114" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+          <t>WM-SP-Monitor Arms- Defensive</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>B0FHVWHQHR</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>14.67</v>
+        <v>77.34</v>
       </c>
       <c r="E115" t="n">
+        <v>6</v>
+      </c>
+      <c r="F115" t="n">
+        <v>899</v>
+      </c>
+      <c r="G115" t="n">
+        <v>2626.27</v>
+      </c>
+      <c r="H115" t="n">
         <v>1</v>
-      </c>
-      <c r="F115" t="n">
-        <v>599</v>
-      </c>
-      <c r="G115" t="n">
-        <v>0</v>
-      </c>
-      <c r="H115" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - PT</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>B0FN4D3C89</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>225.02</v>
+        <v>1575.26</v>
       </c>
       <c r="E116" t="n">
-        <v>11</v>
+        <v>100</v>
       </c>
       <c r="F116" t="n">
-        <v>1703</v>
+        <v>7214</v>
       </c>
       <c r="G116" t="n">
-        <v>363.56</v>
+        <v>11860.16</v>
       </c>
       <c r="H116" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - Phrase</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>B0FN4DSQ6P</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>259.22</v>
+        <v>2509.5</v>
       </c>
       <c r="E117" t="n">
-        <v>9</v>
+        <v>122</v>
       </c>
       <c r="F117" t="n">
-        <v>827</v>
+        <v>8881</v>
       </c>
       <c r="G117" t="n">
-        <v>490.68</v>
+        <v>8911.870000000001</v>
       </c>
       <c r="H117" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 -Phrase</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>B0FN4HDM6Z</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>401.09</v>
+        <v>2755.64</v>
       </c>
       <c r="E118" t="n">
-        <v>17</v>
+        <v>152</v>
       </c>
       <c r="F118" t="n">
-        <v>457</v>
+        <v>27077</v>
       </c>
       <c r="G118" t="n">
-        <v>1778.81</v>
+        <v>1795.76</v>
       </c>
       <c r="H118" t="n">
         <v>1</v>
@@ -3740,106 +3740,106 @@
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
+          <t>WM-SP-POS stand- Multi - PT</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>B0FN4D3C89</t>
+          <t>B0FN4FPJ83</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>441.84</v>
+        <v>10.04</v>
       </c>
       <c r="E119" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="F119" t="n">
-        <v>4751</v>
+        <v>18</v>
       </c>
       <c r="G119" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
+          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>B0FN4DSQ6P</t>
+          <t>B0FN4D3C89</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>73.84999999999999</v>
+        <v>0</v>
       </c>
       <c r="E120" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>1228</v>
+        <v>0</v>
       </c>
       <c r="G120" t="n">
-        <v>1599.16</v>
+        <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
-          <t>WM_SP_KT_Adjustable_Exact_Manual_HV</t>
+          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0FN4DSQ6P</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1473.79</v>
+        <v>1042.42</v>
       </c>
       <c r="E121" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F121" t="n">
-        <v>29827</v>
+        <v>8951</v>
       </c>
       <c r="G121" t="n">
-        <v>12712.71</v>
+        <v>2326.28</v>
       </c>
       <c r="H121" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
-          <t>White Mulberry-Lshape-SP-KT-Phrase</t>
+          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0FN4HDM6Z</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>0</v>
+        <v>598.99</v>
       </c>
       <c r="E122" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F122" t="n">
-        <v>32</v>
+        <v>3460</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3852,22 +3852,22 @@
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
-          <t>White Mulberry-Lshape-SP-KT-Phrase</t>
+          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0FHVWHQHR</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>6.08</v>
+        <v>6.68</v>
       </c>
       <c r="E123" t="n">
         <v>1</v>
       </c>
       <c r="F123" t="n">
-        <v>47</v>
+        <v>864</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3880,50 +3880,50 @@
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>White Mulberry-Motorized-SP-KT-BM</t>
+          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0FN4D3C89</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>171.29</v>
+        <v>449.69</v>
       </c>
       <c r="E124" t="n">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="F124" t="n">
-        <v>1408</v>
+        <v>8638</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>1835.6</v>
       </c>
       <c r="H124" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
-          <t>White Mulberry-Motorized-SP-KT-BM</t>
+          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0FN4DSQ6P</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>0</v>
+        <v>106.69</v>
       </c>
       <c r="E125" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F125" t="n">
-        <v>214</v>
+        <v>5077</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3936,27 +3936,279 @@
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
+          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>B0FHVWHQHR</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>68.55</v>
+      </c>
+      <c r="E126" t="n">
+        <v>4</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1985</v>
+      </c>
+      <c r="G126" t="n">
+        <v>490.68</v>
+      </c>
+      <c r="H126" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr"/>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>B0FN4D3C89</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>303.75</v>
+      </c>
+      <c r="E127" t="n">
+        <v>15</v>
+      </c>
+      <c r="F127" t="n">
+        <v>1920</v>
+      </c>
+      <c r="G127" t="n">
+        <v>727.12</v>
+      </c>
+      <c r="H127" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr"/>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>B0FN4DSQ6P</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>1056.31</v>
+      </c>
+      <c r="E128" t="n">
+        <v>36</v>
+      </c>
+      <c r="F128" t="n">
+        <v>3315</v>
+      </c>
+      <c r="G128" t="n">
+        <v>3434.76</v>
+      </c>
+      <c r="H128" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr"/>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>B0FN4HDM6Z</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>636.1899999999999</v>
+      </c>
+      <c r="E129" t="n">
+        <v>27</v>
+      </c>
+      <c r="F129" t="n">
+        <v>1033</v>
+      </c>
+      <c r="G129" t="n">
+        <v>1778.81</v>
+      </c>
+      <c r="H129" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr"/>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>B0FN4D3C89</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>563.4300000000001</v>
+      </c>
+      <c r="E130" t="n">
+        <v>50</v>
+      </c>
+      <c r="F130" t="n">
+        <v>6152</v>
+      </c>
+      <c r="G130" t="n">
+        <v>2727.12</v>
+      </c>
+      <c r="H130" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr"/>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>B0FN4DSQ6P</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>613.12</v>
+      </c>
+      <c r="E131" t="n">
+        <v>51</v>
+      </c>
+      <c r="F131" t="n">
+        <v>10704</v>
+      </c>
+      <c r="G131" t="n">
+        <v>6996.639999999999</v>
+      </c>
+      <c r="H131" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr"/>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>WM_SP_KT_Adjustable_Exact_Manual_HV</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>B0CPT3Q25C</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>3286.29</v>
+      </c>
+      <c r="E132" t="n">
+        <v>131</v>
+      </c>
+      <c r="F132" t="n">
+        <v>89428</v>
+      </c>
+      <c r="G132" t="n">
+        <v>12712.71</v>
+      </c>
+      <c r="H132" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr"/>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>White Mulberry-Motorized-SP-KT-BM</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>B0CPT3Q25C</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>1221.24</v>
+      </c>
+      <c r="E133" t="n">
+        <v>75</v>
+      </c>
+      <c r="F133" t="n">
+        <v>13109</v>
+      </c>
+      <c r="G133" t="n">
+        <v>12712.71</v>
+      </c>
+      <c r="H133" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr"/>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>White Mulberry-Motorized-SP-KT-BM</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>B0DQ4YWSMC</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>625.12</v>
+      </c>
+      <c r="E134" t="n">
+        <v>33</v>
+      </c>
+      <c r="F134" t="n">
+        <v>10232</v>
+      </c>
+      <c r="G134" t="n">
+        <v>12712.71</v>
+      </c>
+      <c r="H134" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr"/>
+      <c r="B135" t="inlineStr">
+        <is>
           <t>White-B0FN81FD8M-monitor arm (high price)-SP-KT-Phrase</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
+      <c r="C135" t="inlineStr">
         <is>
           <t>B0FN81FD8M</t>
         </is>
       </c>
-      <c r="D126" t="n">
-        <v>26.26</v>
-      </c>
-      <c r="E126" t="n">
-        <v>2</v>
-      </c>
-      <c r="F126" t="n">
-        <v>383</v>
-      </c>
-      <c r="G126" t="n">
-        <v>0</v>
-      </c>
-      <c r="H126" t="n">
+      <c r="D135" t="n">
+        <v>122.41</v>
+      </c>
+      <c r="E135" t="n">
+        <v>8</v>
+      </c>
+      <c r="F135" t="n">
+        <v>1616</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4253,13 +4505,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>213.94</v>
+        <v>308.28</v>
       </c>
       <c r="E10" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F10" t="n">
-        <v>9607</v>
+        <v>14698</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -4281,13 +4533,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>361.06</v>
+        <v>694.3199999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="F11" t="n">
-        <v>15188</v>
+        <v>25301</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -4365,13 +4617,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>420.38</v>
+        <v>1049.38</v>
       </c>
       <c r="E14" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="F14" t="n">
-        <v>19468</v>
+        <v>45409</v>
       </c>
       <c r="G14" t="n">
         <v>2783.9</v>
@@ -4393,19 +4645,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>282.95</v>
+        <v>553.02</v>
       </c>
       <c r="E15" t="n">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="F15" t="n">
-        <v>11435</v>
+        <v>21758</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2626.27</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4503,7 +4755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4566,13 +4818,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3333333333333333</v>
+        <v>2.708333333333333</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -4599,13 +4851,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3333333333333333</v>
+        <v>2.708333333333333</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -4632,13 +4884,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3333333333333333</v>
+        <v>2.708333333333333</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -4665,13 +4917,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3333333333333333</v>
+        <v>2.708333333333333</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -4698,13 +4950,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3333333333333333</v>
+        <v>2.708333333333333</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -4731,13 +4983,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3333333333333333</v>
+        <v>2.708333333333333</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -4962,19 +5214,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2914</v>
+        <v>3617</v>
       </c>
       <c r="E14" t="n">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="F14" t="n">
-        <v>273.555</v>
+        <v>342.3705162078417</v>
       </c>
       <c r="G14" t="n">
-        <v>10761.44</v>
+        <v>19440.3836331897</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -4991,23 +5243,23 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2914</v>
+        <v>1809</v>
       </c>
       <c r="E15" t="n">
-        <v>120</v>
+        <v>74</v>
       </c>
       <c r="F15" t="n">
-        <v>273.555</v>
+        <v>171.1852581039208</v>
       </c>
       <c r="G15" t="n">
-        <v>10761.44</v>
+        <v>9720.191816594852</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -5019,28 +5271,28 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
+          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1822</v>
+        <v>9205</v>
       </c>
       <c r="E16" t="n">
-        <v>35</v>
+        <v>375</v>
       </c>
       <c r="F16" t="n">
-        <v>248.82</v>
+        <v>871.3042256882374</v>
       </c>
       <c r="G16" t="n">
-        <v>6638.416666666667</v>
+        <v>49474.14455021545</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -5057,23 +5309,23 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0DQ1NV8D2</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1822</v>
+        <v>11047</v>
       </c>
       <c r="E17" t="n">
-        <v>35</v>
+        <v>187</v>
       </c>
       <c r="F17" t="n">
-        <v>248.82</v>
+        <v>1463.14</v>
       </c>
       <c r="G17" t="n">
-        <v>6638.416666666667</v>
+        <v>32627.96</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -5085,25 +5337,25 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
+          <t>SB-Lshape-Multi Asin- KT- phrase</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1822</v>
+        <v>1560</v>
       </c>
       <c r="E18" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="F18" t="n">
-        <v>248.82</v>
+        <v>257.44</v>
       </c>
       <c r="G18" t="n">
-        <v>6638.416666666667</v>
+        <v>7075.42</v>
       </c>
       <c r="H18" t="n">
         <v>1</v>
@@ -5127,19 +5379,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4554</v>
+        <v>9999</v>
       </c>
       <c r="E19" t="n">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="F19" t="n">
-        <v>637.09</v>
+        <v>1265.03</v>
       </c>
       <c r="G19" t="n">
-        <v>2626.27</v>
+        <v>5252.54</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -5160,13 +5412,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>9474</v>
+        <v>19416</v>
       </c>
       <c r="E20" t="n">
-        <v>92</v>
+        <v>202</v>
       </c>
       <c r="F20" t="n">
-        <v>1295.72</v>
+        <v>2717.31</v>
       </c>
       <c r="G20" t="n">
         <v>5579.66</v>
@@ -5193,13 +5445,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>0.54</v>
+        <v>4.718333333333333</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -5226,13 +5478,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>0.54</v>
+        <v>4.718333333333333</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -5259,13 +5511,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>0.54</v>
+        <v>4.718333333333333</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -5292,13 +5544,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>0.54</v>
+        <v>4.718333333333333</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -5325,13 +5577,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>0.54</v>
+        <v>4.718333333333333</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -5358,13 +5610,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>0.54</v>
+        <v>4.718333333333333</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -5391,19 +5643,19 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>634</v>
+        <v>3803</v>
       </c>
       <c r="E27" t="n">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="F27" t="n">
-        <v>102.1883333333333</v>
+        <v>613.13</v>
       </c>
       <c r="G27" t="n">
-        <v>388.2766666666666</v>
+        <v>2329.66</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -5415,195 +5667,30 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Defensive</t>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>634</v>
+        <v>17301</v>
       </c>
       <c r="E28" t="n">
-        <v>10</v>
+        <v>140</v>
       </c>
       <c r="F28" t="n">
-        <v>102.1883333333333</v>
+        <v>2415.43</v>
       </c>
       <c r="G28" t="n">
-        <v>388.2766666666666</v>
+        <v>4659.32</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I28" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>WM-SB-Monitor Arms-Defensive</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>B0DB5W4TCP</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>634</v>
-      </c>
-      <c r="E29" t="n">
-        <v>10</v>
-      </c>
-      <c r="F29" t="n">
-        <v>102.1883333333333</v>
-      </c>
-      <c r="G29" t="n">
-        <v>388.2766666666666</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>WM-SB-Monitor Arms-Defensive</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>B0DB5YTQZV</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>634</v>
-      </c>
-      <c r="E30" t="n">
-        <v>10</v>
-      </c>
-      <c r="F30" t="n">
-        <v>102.1883333333333</v>
-      </c>
-      <c r="G30" t="n">
-        <v>388.2766666666666</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>WM-SB-Monitor Arms-Defensive</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>B0DP2Z5DQ9</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>634</v>
-      </c>
-      <c r="E31" t="n">
-        <v>10</v>
-      </c>
-      <c r="F31" t="n">
-        <v>102.1883333333333</v>
-      </c>
-      <c r="G31" t="n">
-        <v>388.2766666666666</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>WM-SB-Monitor Arms-Defensive</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>B0DP32F346</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>634</v>
-      </c>
-      <c r="E32" t="n">
-        <v>10</v>
-      </c>
-      <c r="F32" t="n">
-        <v>102.1883333333333</v>
-      </c>
-      <c r="G32" t="n">
-        <v>388.2766666666666</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>7908</v>
-      </c>
-      <c r="E33" t="n">
-        <v>55</v>
-      </c>
-      <c r="F33" t="n">
-        <v>950.28</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="inlineStr">
         <is>
           <t>White Mulberry</t>
         </is>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week23.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week23.xlsx
@@ -4539,7 +4539,7 @@
         <v>77</v>
       </c>
       <c r="F11" t="n">
-        <v>25301</v>
+        <v>25300</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -4651,7 +4651,7 @@
         <v>72</v>
       </c>
       <c r="F15" t="n">
-        <v>21758</v>
+        <v>21757</v>
       </c>
       <c r="G15" t="n">
         <v>2626.27</v>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week23.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week23.xlsx
@@ -1319,7 +1319,7 @@
         <v>19</v>
       </c>
       <c r="F32" t="n">
-        <v>6347</v>
+        <v>6346</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1347,7 +1347,7 @@
         <v>43</v>
       </c>
       <c r="F33" t="n">
-        <v>6394</v>
+        <v>6393</v>
       </c>
       <c r="G33" t="n">
         <v>22032.2</v>
@@ -1375,7 +1375,7 @@
         <v>7</v>
       </c>
       <c r="F34" t="n">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2747.24</v>
+        <v>2734.84</v>
       </c>
       <c r="E52" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F52" t="n">
-        <v>30514</v>
+        <v>30513</v>
       </c>
       <c r="G52" t="n">
         <v>7202.54</v>
@@ -2187,7 +2187,7 @@
         <v>90</v>
       </c>
       <c r="F63" t="n">
-        <v>10841</v>
+        <v>10838</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
         <v>139</v>
       </c>
       <c r="F72" t="n">
-        <v>19932</v>
+        <v>19930</v>
       </c>
       <c r="G72" t="n">
         <v>3388.14</v>
@@ -2551,7 +2551,7 @@
         <v>83</v>
       </c>
       <c r="F76" t="n">
-        <v>11634</v>
+        <v>11633</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2803,7 +2803,7 @@
         <v>62</v>
       </c>
       <c r="F85" t="n">
-        <v>7834</v>
+        <v>7833</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -3195,7 +3195,7 @@
         <v>146</v>
       </c>
       <c r="F99" t="n">
-        <v>26346</v>
+        <v>26345</v>
       </c>
       <c r="G99" t="n">
         <v>15025.44</v>
@@ -3447,7 +3447,7 @@
         <v>15</v>
       </c>
       <c r="F108" t="n">
-        <v>5165</v>
+        <v>5164</v>
       </c>
       <c r="G108" t="n">
         <v>7202.54</v>
@@ -3475,7 +3475,7 @@
         <v>12</v>
       </c>
       <c r="F109" t="n">
-        <v>4433</v>
+        <v>4432</v>
       </c>
       <c r="G109" t="n">
         <v>7944.92</v>
@@ -3587,7 +3587,7 @@
         <v>37</v>
       </c>
       <c r="F113" t="n">
-        <v>5669</v>
+        <v>5668</v>
       </c>
       <c r="G113" t="n">
         <v>1694.07</v>
@@ -3643,7 +3643,7 @@
         <v>6</v>
       </c>
       <c r="F115" t="n">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="G115" t="n">
         <v>2626.27</v>
@@ -3671,7 +3671,7 @@
         <v>100</v>
       </c>
       <c r="F116" t="n">
-        <v>7214</v>
+        <v>7211</v>
       </c>
       <c r="G116" t="n">
         <v>11860.16</v>
@@ -3699,7 +3699,7 @@
         <v>122</v>
       </c>
       <c r="F117" t="n">
-        <v>8881</v>
+        <v>8880</v>
       </c>
       <c r="G117" t="n">
         <v>8911.870000000001</v>
@@ -4511,7 +4511,7 @@
         <v>32</v>
       </c>
       <c r="F10" t="n">
-        <v>14698</v>
+        <v>14697</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -4651,7 +4651,7 @@
         <v>72</v>
       </c>
       <c r="F15" t="n">
-        <v>21757</v>
+        <v>21755</v>
       </c>
       <c r="G15" t="n">
         <v>2626.27</v>
@@ -5412,7 +5412,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>19416</v>
+        <v>19414</v>
       </c>
       <c r="E20" t="n">
         <v>202</v>
@@ -5676,7 +5676,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>17301</v>
+        <v>17299</v>
       </c>
       <c r="E28" t="n">
         <v>140</v>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week23.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week23.xlsx
@@ -1052,7 +1052,7 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Camb-Motorized-SP-KT-Phrase</t>
+          <t>Camb-Motorized-SP-KT-BM</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1061,26 +1061,26 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>175.77</v>
+        <v>1221.24</v>
       </c>
       <c r="E23" t="n">
-        <v>11</v>
+        <v>75</v>
       </c>
       <c r="F23" t="n">
-        <v>1916</v>
+        <v>13108</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>12712.71</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Camb-Motorized-SP-KT-Phrase</t>
+          <t>Camb-Motorized-SP-KT-BM</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1089,26 +1089,26 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>553.9200000000001</v>
+        <v>625.12</v>
       </c>
       <c r="E24" t="n">
         <v>33</v>
       </c>
       <c r="F24" t="n">
-        <v>18298</v>
+        <v>10232</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>12712.71</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Camb-Motorized-SP-PT-Exact</t>
+          <t>Camb-Motorized-SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1117,13 +1117,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>684.59</v>
+        <v>175.77</v>
       </c>
       <c r="E25" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F25" t="n">
-        <v>3503</v>
+        <v>1916</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1136,7 +1136,7 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Camb-Motorized-SP-PT-Exact</t>
+          <t>Camb-Motorized-SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1145,13 +1145,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>142.62</v>
+        <v>553.9200000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="F26" t="n">
-        <v>1161</v>
+        <v>18298</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1164,22 +1164,22 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Camb-SP- L Shaped-B0BFWD6SNF-Exact &amp; Phrase(2)</t>
+          <t>Camb-Motorized-SP-PT</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>39.07</v>
+        <v>684.59</v>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="F27" t="n">
-        <v>596</v>
+        <v>3503</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1192,22 +1192,22 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Camb-SP-B0BFVNS8HS -L-Shape-Exact-phrase</t>
+          <t>Camb-Motorized-SP-PT</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0BFVNS8HS</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>312.17</v>
+        <v>142.62</v>
       </c>
       <c r="E28" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F28" t="n">
-        <v>7609</v>
+        <v>1161</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1220,22 +1220,22 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Camb-SP-Branded</t>
+          <t>Camb-SP- L Shaped-B0BFWD6SNF-Exact &amp; Phrase(2)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>400.03</v>
+        <v>39.07</v>
       </c>
       <c r="E29" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="F29" t="n">
-        <v>1991</v>
+        <v>596</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1248,7 +1248,7 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Camb-SP-Branded</t>
+          <t>Camb-SP-B0BFVNS8HS -L-Shape-Exact-phrase</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1257,13 +1257,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>27.58</v>
+        <v>312.17</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F30" t="n">
-        <v>2659</v>
+        <v>7609</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1281,17 +1281,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>125.11</v>
+        <v>400.03</v>
       </c>
       <c r="E31" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F31" t="n">
-        <v>1518</v>
+        <v>1991</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1309,17 +1309,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVNS8HS</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>487.19</v>
+        <v>27.58</v>
       </c>
       <c r="E32" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>6346</v>
+        <v>2659</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1337,23 +1337,23 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>852.89</v>
+        <v>125.11</v>
       </c>
       <c r="E33" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="F33" t="n">
-        <v>6393</v>
+        <v>1518</v>
       </c>
       <c r="G33" t="n">
-        <v>22032.2</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1365,17 +1365,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>124.91</v>
+        <v>487.19</v>
       </c>
       <c r="E34" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="F34" t="n">
-        <v>1492</v>
+        <v>6342</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1388,78 +1388,78 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-B0BFVMDJ2K/B0BFWD6SNF- Exact/Phrase</t>
+          <t>Camb-SP-Branded</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>3389.71</v>
+        <v>852.89</v>
       </c>
       <c r="E35" t="n">
-        <v>146</v>
+        <v>43</v>
       </c>
       <c r="F35" t="n">
-        <v>25286</v>
+        <v>6393</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>22032.2</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-B0BFWD6SNF - Broad</t>
+          <t>Camb-SP-Branded</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1052.21</v>
+        <v>124.91</v>
       </c>
       <c r="E36" t="n">
-        <v>115</v>
+        <v>7</v>
       </c>
       <c r="F36" t="n">
-        <v>12849</v>
+        <v>1492</v>
       </c>
       <c r="G36" t="n">
-        <v>49782.18</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-CDesk-Multiple Asin- PT</t>
+          <t>Camb-SP-Lshape-B0BFVMDJ2K/B0BFWD6SNF- Exact/Phrase</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1298.48</v>
+        <v>3389.71</v>
       </c>
       <c r="E37" t="n">
-        <v>46</v>
+        <v>146</v>
       </c>
       <c r="F37" t="n">
-        <v>5566</v>
+        <v>25285</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1472,50 +1472,50 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multi Asin- AT</t>
+          <t>Camb-SP-Lshape-B0BFWD6SNF - Broad</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>263.02</v>
+        <v>1052.21</v>
       </c>
       <c r="E38" t="n">
-        <v>8</v>
+        <v>115</v>
       </c>
       <c r="F38" t="n">
-        <v>960</v>
+        <v>12849</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>49782.18</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multi Asin- AT</t>
+          <t>Camb-SP-Lshape-CDesk-Multiple Asin- PT</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0BFVNS8HS</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>1298.48</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="F39" t="n">
-        <v>40</v>
+        <v>5566</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1533,17 +1533,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>89.8</v>
+        <v>263.02</v>
       </c>
       <c r="E40" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F40" t="n">
-        <v>1095</v>
+        <v>960</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1561,17 +1561,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVNS8HS</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>93.31999999999999</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>1171</v>
+        <v>40</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1584,50 +1584,50 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multiple Asins- Exact 01</t>
+          <t>Camb-SP-Lshape-Multi Asin- AT</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>3157.18</v>
+        <v>89.8</v>
       </c>
       <c r="E42" t="n">
-        <v>149</v>
+        <v>3</v>
       </c>
       <c r="F42" t="n">
-        <v>40736</v>
+        <v>1095</v>
       </c>
       <c r="G42" t="n">
-        <v>13105.08</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multiple Asins- Exact 01</t>
+          <t>Camb-SP-Lshape-Multi Asin- AT</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>462.51</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="E43" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F43" t="n">
-        <v>6918</v>
+        <v>1171</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1640,7 +1640,7 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multiple Asins- Exact/Phrase</t>
+          <t>Camb-SP-Lshape-Multiple Asins- Exact 01</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1649,26 +1649,26 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>358.74</v>
+        <v>3157.18</v>
       </c>
       <c r="E44" t="n">
-        <v>21</v>
+        <v>149</v>
       </c>
       <c r="F44" t="n">
-        <v>3551</v>
+        <v>40735</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>13105.08</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multiple Asins- Exact/Phrase</t>
+          <t>Camb-SP-Lshape-Multiple Asins- Exact 01</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1677,19 +1677,19 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2471.67</v>
+        <v>462.51</v>
       </c>
       <c r="E45" t="n">
-        <v>110</v>
+        <v>20</v>
       </c>
       <c r="F45" t="n">
-        <v>35503</v>
+        <v>6918</v>
       </c>
       <c r="G45" t="n">
-        <v>7075.42</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1701,17 +1701,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>505.04</v>
+        <v>358.74</v>
       </c>
       <c r="E46" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F46" t="n">
-        <v>8532</v>
+        <v>3551</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1724,50 +1724,50 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Camb-SP-Motorized Desk- B0CPT3Q25C- Exact</t>
+          <t>Camb-SP-Lshape-Multiple Asins- Exact/Phrase</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1036.11</v>
+        <v>2471.67</v>
       </c>
       <c r="E47" t="n">
-        <v>27</v>
+        <v>110</v>
       </c>
       <c r="F47" t="n">
-        <v>8965</v>
+        <v>35498</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>7075.42</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Camb-SP-Motorized Desk-B0CPT3Q25C - PT01</t>
+          <t>Camb-SP-Lshape-Multiple Asins- Exact/Phrase</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2398.7</v>
+        <v>505.04</v>
       </c>
       <c r="E48" t="n">
-        <v>103</v>
+        <v>24</v>
       </c>
       <c r="F48" t="n">
-        <v>12424</v>
+        <v>8530</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Camb-SP-Motorized Desk-B0CPT3Q25C- Exact</t>
+          <t>Camb-SP-Motorized Desk- B0CPT3Q25C- Exact</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1717.93</v>
+        <v>1036.11</v>
       </c>
       <c r="E49" t="n">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="F49" t="n">
-        <v>16286</v>
+        <v>8965</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1808,50 +1808,50 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Camb-SP-Zshape-B0CPFS24ML- CT ref</t>
+          <t>Camb-SP-Motorized Desk-B0CPT3Q25C - PT01</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2632.43</v>
+        <v>2398.7</v>
       </c>
       <c r="E50" t="n">
-        <v>147</v>
+        <v>103</v>
       </c>
       <c r="F50" t="n">
-        <v>21973</v>
+        <v>12424</v>
       </c>
       <c r="G50" t="n">
-        <v>21607.62</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Camb-SP-Zshape-B0CPFS24ML- PT</t>
+          <t>Camb-SP-Motorized Desk-B0CPT3Q25C- Exact</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>3018.27</v>
+        <v>1717.93</v>
       </c>
       <c r="E51" t="n">
-        <v>198</v>
+        <v>61</v>
       </c>
       <c r="F51" t="n">
-        <v>14498</v>
+        <v>16286</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1864,7 +1864,7 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Camb-SP-Zshape-B0CPFS24ML- Phrase</t>
+          <t>Camb-SP-Zshape-B0CPFS24ML- CT ref</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1873,26 +1873,26 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2734.84</v>
+        <v>2632.43</v>
       </c>
       <c r="E52" t="n">
-        <v>217</v>
+        <v>147</v>
       </c>
       <c r="F52" t="n">
-        <v>30513</v>
+        <v>21973</v>
       </c>
       <c r="G52" t="n">
-        <v>7202.54</v>
+        <v>21607.62</v>
       </c>
       <c r="H52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Camb-SP-Zshape-B0CPFS24ML-PT01</t>
+          <t>Camb-SP-Zshape-B0CPFS24ML- PT</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1901,54 +1901,54 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1867.73</v>
+        <v>3018.27</v>
       </c>
       <c r="E53" t="n">
-        <v>97</v>
+        <v>198</v>
       </c>
       <c r="F53" t="n">
-        <v>6225</v>
+        <v>14498</v>
       </c>
       <c r="G53" t="n">
-        <v>11016.1</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Camb-SP-stand desk- B0DQ1NV8D2- PT</t>
+          <t>Camb-SP-Zshape-B0CPFS24ML- Phrase</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1826.2</v>
+        <v>2734.84</v>
       </c>
       <c r="E54" t="n">
-        <v>51</v>
+        <v>217</v>
       </c>
       <c r="F54" t="n">
-        <v>6032</v>
+        <v>30513</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>7202.54</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Camb-Zshape-Gaming- B0CPFS24ML-Phrase/Exact</t>
+          <t>Camb-SP-Zshape-B0CPFS24ML-PT01</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1957,54 +1957,54 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>3603.81</v>
+        <v>1867.73</v>
       </c>
       <c r="E55" t="n">
-        <v>347</v>
+        <v>97</v>
       </c>
       <c r="F55" t="n">
-        <v>45883</v>
+        <v>6225</v>
       </c>
       <c r="G55" t="n">
-        <v>14405.08</v>
+        <v>11016.1</v>
       </c>
       <c r="H55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SP CT PT_B0CPFS24ML_Gaming</t>
+          <t>Camb-SP-stand desk- B0DQ1NV8D2- PT</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2526.64</v>
+        <v>1826.2</v>
       </c>
       <c r="E56" t="n">
-        <v>246</v>
+        <v>51</v>
       </c>
       <c r="F56" t="n">
-        <v>19145</v>
+        <v>6032</v>
       </c>
       <c r="G56" t="n">
-        <v>14405.08</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SP KT_B0CPFS24ML_Manual_Gaming</t>
+          <t>Camb-Zshape-Gaming- B0CPFS24ML-Phrase/Exact</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2013,69 +2013,69 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1154.3</v>
+        <v>3603.81</v>
       </c>
       <c r="E57" t="n">
-        <v>68</v>
+        <v>347</v>
       </c>
       <c r="F57" t="n">
-        <v>5915</v>
+        <v>45882</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>14405.08</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SP_KT_L shape Non Performing Ex</t>
+          <t>SP CT PT_B0CPFS24ML_Gaming</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>185.02</v>
+        <v>2526.64</v>
       </c>
       <c r="E58" t="n">
-        <v>10</v>
+        <v>246</v>
       </c>
       <c r="F58" t="n">
-        <v>2635</v>
+        <v>19140</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>14405.08</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SP_KT_L shape Non Performing Ex</t>
+          <t>SP KT_B0CPFS24ML_Manual_Gaming</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>231.9</v>
+        <v>1154.3</v>
       </c>
       <c r="E59" t="n">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="F59" t="n">
-        <v>3142</v>
+        <v>5915</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -2093,17 +2093,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>228.14</v>
+        <v>185.02</v>
       </c>
       <c r="E60" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F60" t="n">
-        <v>4240</v>
+        <v>2635</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2116,22 +2116,22 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SP_PT_L shape Non Performing PT</t>
+          <t>SP_KT_L shape Non Performing Ex</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>993.91</v>
+        <v>231.9</v>
       </c>
       <c r="E61" t="n">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="F61" t="n">
-        <v>3099</v>
+        <v>3142</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2144,7 +2144,7 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SP_PT_L shape Non Performing PT</t>
+          <t>SP_KT_L shape Non Performing Ex</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2153,13 +2153,13 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>841.9100000000001</v>
+        <v>228.14</v>
       </c>
       <c r="E62" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F62" t="n">
-        <v>6758</v>
+        <v>4240</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2172,22 +2172,22 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>WB- SP- B0DB5VG39T - PT</t>
+          <t>SP_PT_L shape Non Performing PT</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1811.25</v>
+        <v>993.91</v>
       </c>
       <c r="E63" t="n">
-        <v>90</v>
+        <v>47</v>
       </c>
       <c r="F63" t="n">
-        <v>10838</v>
+        <v>3097</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2200,22 +2200,22 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>WB- SP- B0DB5YTQZV-B0DB5VVPSB- PT</t>
+          <t>SP_PT_L shape Non Performing PT</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>841.9100000000001</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>6758</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2228,22 +2228,22 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>WB- SP- B0DB5YTQZV-B0DB5VVPSB- PT</t>
+          <t>WB- SP- B0DB5VG39T - PT</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>1811.25</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>10838</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2256,22 +2256,22 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>WB- SP- B0DP2VVRND - PT</t>
+          <t>WB- SP- B0DB5YTQZV-B0DB5VVPSB- PT</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>B0DP2VVRND</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>249.31</v>
+        <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>440</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2284,22 +2284,22 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>WB- SP- B0DP2WC5VW - PT</t>
+          <t>WB- SP- B0DB5YTQZV-B0DB5VVPSB- PT</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>175.15</v>
+        <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>264</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2312,50 +2312,50 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>WB- SP- B0DP32F346 - PT</t>
+          <t>WB- SP- B0DP2VVRND - PT</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DP2VVRND</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>2040.75</v>
+        <v>249.31</v>
       </c>
       <c r="E68" t="n">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="F68" t="n">
-        <v>6587</v>
+        <v>440</v>
       </c>
       <c r="G68" t="n">
-        <v>2626.27</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>WB- SP-B0DB5W4TCP-PT</t>
+          <t>WB- SP- B0DP2WC5VW - PT</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>175.15</v>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>264</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2368,40 +2368,40 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>WM- Adj Metal desk- B0DB5W4TCP-SP-KT-Phrase</t>
+          <t>WB- SP- B0DP32F346 - PT</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>394.12</v>
+        <v>2040.75</v>
       </c>
       <c r="E70" t="n">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="F70" t="n">
-        <v>2208</v>
+        <v>6587</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>2626.27</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>WM- Height Adj stand - B0DP2VVRND-SP-KT-Phrase</t>
+          <t>WB- SP-B0DB5W4TCP-PT</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>B0DP2VVRND</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2424,91 +2424,91 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>WM- Height Adj stand Dual-B0DB5YTQZV-SP-KT-Phrase/BM</t>
+          <t>WM- Adj Metal desk- B0DB5W4TCP-SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>3059.83</v>
+        <v>394.12</v>
       </c>
       <c r="E72" t="n">
-        <v>139</v>
+        <v>10</v>
       </c>
       <c r="F72" t="n">
-        <v>19930</v>
+        <v>2208</v>
       </c>
       <c r="G72" t="n">
-        <v>3388.14</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>WM- Height Adjustable stand- Dual-B0DB5YTQZV- PT</t>
+          <t>WM- Height Adj stand - B0DP2VVRND-SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP2VVRND</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>2202.9</v>
+        <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>3251</v>
+        <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>10829.66</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>WM- SP- Adj Metal desk- Multi Asins- PT</t>
+          <t>WM- Height Adj stand Dual-B0DB5YTQZV-SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1021.35</v>
+        <v>3059.83</v>
       </c>
       <c r="E74" t="n">
-        <v>47</v>
+        <v>139</v>
       </c>
       <c r="F74" t="n">
-        <v>7617</v>
+        <v>19930</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>3388.14</v>
       </c>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>WM- SP- Adj Metal desk- Multi Asins- PT</t>
+          <t>WM- Height Adjustable stand- Dual-B0DB5YTQZV- PT</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2517,41 +2517,41 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>2202.9</v>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>3251</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>10829.66</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>WM- SP- Height Adjustable stand- Dual-B0DB5YTQZV- Broad</t>
+          <t>WM- SP- Adj Metal desk- Multi Asins- PT</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>941.77</v>
+        <v>1021.35</v>
       </c>
       <c r="E76" t="n">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="F76" t="n">
-        <v>11633</v>
+        <v>7617</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2564,63 +2564,63 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>WM- SP- Wall Mounted Stand- B0DP2WC5VW- Broad</t>
+          <t>WM- SP- Adj Metal desk- Multi Asins- PT</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>444.67</v>
+        <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>3484</v>
+        <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>2795.76</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>WM- SP- Wooden Arm- B0DP32F346- PT</t>
+          <t>WM- SP- Height Adjustable stand- Dual-B0DB5YTQZV- Broad</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>2608.73</v>
+        <v>941.77</v>
       </c>
       <c r="E78" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F78" t="n">
-        <v>16332</v>
+        <v>11633</v>
       </c>
       <c r="G78" t="n">
-        <v>12934.37</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>WM- SP-Wall Mounted Stand- B0DP2WC5VW- Exact &amp; Phrase</t>
+          <t>WM- SP- Wall Mounted Stand- B0DP2WC5VW- Broad</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2629,54 +2629,54 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1156.38</v>
+        <v>444.67</v>
       </c>
       <c r="E79" t="n">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="F79" t="n">
-        <v>2912</v>
+        <v>3484</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>2795.76</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>WM- Wall Mounted Stand- B0DP2WC5VW- PT</t>
+          <t>WM- SP- Wooden Arm- B0DP32F346- PT</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>859.1600000000001</v>
+        <v>2608.73</v>
       </c>
       <c r="E80" t="n">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="F80" t="n">
-        <v>2540</v>
+        <v>16332</v>
       </c>
       <c r="G80" t="n">
-        <v>8375.42</v>
+        <v>12934.37</v>
       </c>
       <c r="H80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>WM- Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
+          <t>WM- SP-Wall Mounted Stand- B0DP2WC5VW- Exact &amp; Phrase</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2685,26 +2685,26 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1959.49</v>
+        <v>1156.38</v>
       </c>
       <c r="E81" t="n">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="F81" t="n">
-        <v>10655</v>
+        <v>2912</v>
       </c>
       <c r="G81" t="n">
-        <v>8375.42</v>
+        <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>WM- Wall Mounted Stand- B0DP2WC5VW- SP-KT-Phrase/BM</t>
+          <t>WM- Wall Mounted Stand- B0DP2WC5VW- PT</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2713,59 +2713,59 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>859.1600000000001</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>2540</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>8375.42</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>WM-Gas Spring MA- B0DB5VG39T-SP-KT-Phrase/BM</t>
+          <t>WM- Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>2534.24</v>
+        <v>1959.49</v>
       </c>
       <c r="E83" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F83" t="n">
-        <v>11393</v>
+        <v>10655</v>
       </c>
       <c r="G83" t="n">
-        <v>2329.66</v>
+        <v>8375.42</v>
       </c>
       <c r="H83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>WM-Gas Spring MA- Dual - B0DB5VVPSB-SP-KT-Phrase/BM</t>
+          <t>WM- Wall Mounted Stand- B0DP2WC5VW- SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -2788,56 +2788,56 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
+          <t>WM-Gas Spring MA- B0DB5VG39T-SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1135.44</v>
+        <v>2534.24</v>
       </c>
       <c r="E85" t="n">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F85" t="n">
-        <v>7833</v>
+        <v>11393</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>2329.66</v>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
+          <t>WM-Gas Spring MA- Dual - B0DB5VVPSB-SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>565.67</v>
+        <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>12969</v>
+        <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>2965.25</v>
+        <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -2849,17 +2849,17 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>653.38</v>
+        <v>1135.44</v>
       </c>
       <c r="E87" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="F87" t="n">
-        <v>16094</v>
+        <v>7833</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2877,79 +2877,79 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>534.4300000000001</v>
+        <v>565.67</v>
       </c>
       <c r="E88" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F88" t="n">
-        <v>19329</v>
+        <v>12969</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>2965.25</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>517.61</v>
+        <v>653.38</v>
       </c>
       <c r="E89" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F89" t="n">
-        <v>4120</v>
+        <v>16094</v>
       </c>
       <c r="G89" t="n">
-        <v>2932.2</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1014.82</v>
+        <v>534.4300000000001</v>
       </c>
       <c r="E90" t="n">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="F90" t="n">
-        <v>5140</v>
+        <v>19329</v>
       </c>
       <c r="G90" t="n">
-        <v>2783.9</v>
+        <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -2961,20 +2961,20 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1102.53</v>
+        <v>517.61</v>
       </c>
       <c r="E91" t="n">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="F91" t="n">
-        <v>7319</v>
+        <v>4120</v>
       </c>
       <c r="G91" t="n">
-        <v>5155.93</v>
+        <v>2932.2</v>
       </c>
       <c r="H91" t="n">
         <v>2</v>
@@ -2989,73 +2989,73 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>229.8</v>
+        <v>1014.82</v>
       </c>
       <c r="E92" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="F92" t="n">
-        <v>2225</v>
+        <v>5140</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>2783.9</v>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - exact</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>1102.53</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>7319</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>5155.93</v>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - exact</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>859.26</v>
+        <v>229.8</v>
       </c>
       <c r="E94" t="n">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="F94" t="n">
-        <v>17573</v>
+        <v>2225</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -3068,12 +3068,12 @@
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>WM-SP- Premium Monitor Arms- Multi Asins -Phrase</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - exact</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>B0DP3194QN</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3096,22 +3096,22 @@
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>WM-SP- Premium Monitor Arms- Multi Asins -Phrase</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - exact</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>2452.04</v>
+        <v>859.26</v>
       </c>
       <c r="E96" t="n">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="F96" t="n">
-        <v>22496</v>
+        <v>17572</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -3124,22 +3124,22 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring -Multi Asins- Phrase &amp; Exact</t>
+          <t>WM-SP- Premium Monitor Arms- Multi Asins -Phrase</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DP3194QN</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>2528.17</v>
+        <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>51448</v>
+        <v>0</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -3152,22 +3152,22 @@
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring -Multi Asins- Phrase &amp; Exact</t>
+          <t>WM-SP- Premium Monitor Arms- Multi Asins -Phrase</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0</v>
+        <v>2452.04</v>
       </c>
       <c r="E98" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>22495</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -3180,7 +3180,7 @@
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T- Broad</t>
+          <t>WM-SP-Gas Spring -Multi Asins- Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3189,31 +3189,31 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>2147.19</v>
+        <v>2528.17</v>
       </c>
       <c r="E99" t="n">
-        <v>146</v>
+        <v>112</v>
       </c>
       <c r="F99" t="n">
-        <v>26345</v>
+        <v>51447</v>
       </c>
       <c r="G99" t="n">
-        <v>15025.44</v>
+        <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T- Exact &amp; Phrase</t>
+          <t>WM-SP-Gas Spring -Multi Asins- Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3236,7 +3236,7 @@
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T- Broad</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3245,47 +3245,47 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1556.37</v>
+        <v>2147.19</v>
       </c>
       <c r="E101" t="n">
-        <v>53</v>
+        <v>146</v>
       </c>
       <c r="F101" t="n">
-        <v>2409</v>
+        <v>26343</v>
       </c>
       <c r="G101" t="n">
-        <v>6141.52</v>
+        <v>15025.44</v>
       </c>
       <c r="H101" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T- Exact &amp; Phrase</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>852.29</v>
+        <v>0</v>
       </c>
       <c r="E102" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>2473</v>
+        <v>0</v>
       </c>
       <c r="G102" t="n">
-        <v>4151.69</v>
+        <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -3297,48 +3297,48 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>134.76</v>
+        <v>1556.37</v>
       </c>
       <c r="E103" t="n">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="F103" t="n">
-        <v>691</v>
+        <v>2409</v>
       </c>
       <c r="G103" t="n">
-        <v>2372.03</v>
+        <v>6141.52</v>
       </c>
       <c r="H103" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Branded</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>586.49</v>
+        <v>852.29</v>
       </c>
       <c r="E104" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F104" t="n">
-        <v>7351</v>
+        <v>2473</v>
       </c>
       <c r="G104" t="n">
-        <v>2329.66</v>
+        <v>4151.69</v>
       </c>
       <c r="H104" t="n">
         <v>1</v>
@@ -3348,28 +3348,28 @@
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Branded</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>176.9</v>
+        <v>134.76</v>
       </c>
       <c r="E105" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F105" t="n">
-        <v>1660</v>
+        <v>691</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>2372.03</v>
       </c>
       <c r="H105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -3381,23 +3381,23 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>206.6</v>
+        <v>586.49</v>
       </c>
       <c r="E106" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F106" t="n">
-        <v>2753</v>
+        <v>7351</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>2329.66</v>
       </c>
       <c r="H106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -3409,17 +3409,17 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>86.90000000000001</v>
+        <v>176.9</v>
       </c>
       <c r="E107" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F107" t="n">
-        <v>1936</v>
+        <v>1660</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3437,23 +3437,23 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>254.5</v>
+        <v>206.6</v>
       </c>
       <c r="E108" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F108" t="n">
-        <v>5164</v>
+        <v>2753</v>
       </c>
       <c r="G108" t="n">
-        <v>7202.54</v>
+        <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -3465,79 +3465,79 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>173.56</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="E109" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F109" t="n">
-        <v>4432</v>
+        <v>1936</v>
       </c>
       <c r="G109" t="n">
-        <v>7944.92</v>
+        <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Defensive</t>
+          <t>WM-SP-Monitor Arms- Branded</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>161.18</v>
+        <v>254.5</v>
       </c>
       <c r="E110" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F110" t="n">
-        <v>1131</v>
+        <v>5163</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>7202.54</v>
       </c>
       <c r="H110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Defensive</t>
+          <t>WM-SP-Monitor Arms- Branded</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>257.39</v>
+        <v>173.56</v>
       </c>
       <c r="E111" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F111" t="n">
-        <v>3064</v>
+        <v>4431</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>7944.92</v>
       </c>
       <c r="H111" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -3549,17 +3549,17 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>135.68</v>
+        <v>161.18</v>
       </c>
       <c r="E112" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F112" t="n">
-        <v>1240</v>
+        <v>1131</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3577,23 +3577,23 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>469.36</v>
+        <v>257.39</v>
       </c>
       <c r="E113" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="F113" t="n">
-        <v>5668</v>
+        <v>3064</v>
       </c>
       <c r="G113" t="n">
-        <v>1694.07</v>
+        <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -3605,23 +3605,23 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>517.54</v>
+        <v>135.68</v>
       </c>
       <c r="E114" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="F114" t="n">
-        <v>5793</v>
+        <v>1240</v>
       </c>
       <c r="G114" t="n">
-        <v>4744.07</v>
+        <v>0</v>
       </c>
       <c r="H114" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -3633,20 +3633,20 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>77.34</v>
+        <v>469.36</v>
       </c>
       <c r="E115" t="n">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="F115" t="n">
-        <v>898</v>
+        <v>5668</v>
       </c>
       <c r="G115" t="n">
-        <v>2626.27</v>
+        <v>1694.07</v>
       </c>
       <c r="H115" t="n">
         <v>1</v>
@@ -3656,7 +3656,7 @@
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - PT</t>
+          <t>WM-SP-Monitor Arms- Defensive</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3665,54 +3665,54 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1575.26</v>
+        <v>517.54</v>
       </c>
       <c r="E116" t="n">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="F116" t="n">
-        <v>7211</v>
+        <v>5793</v>
       </c>
       <c r="G116" t="n">
-        <v>11860.16</v>
+        <v>4744.07</v>
       </c>
       <c r="H116" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - Phrase</t>
+          <t>WM-SP-Monitor Arms- Defensive</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>2509.5</v>
+        <v>77.34</v>
       </c>
       <c r="E117" t="n">
-        <v>122</v>
+        <v>6</v>
       </c>
       <c r="F117" t="n">
-        <v>8880</v>
+        <v>898</v>
       </c>
       <c r="G117" t="n">
-        <v>8911.870000000001</v>
+        <v>2626.27</v>
       </c>
       <c r="H117" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 -Phrase</t>
+          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - PT</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3721,103 +3721,103 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>2755.64</v>
+        <v>1575.26</v>
       </c>
       <c r="E118" t="n">
-        <v>152</v>
+        <v>100</v>
       </c>
       <c r="F118" t="n">
-        <v>27077</v>
+        <v>7211</v>
       </c>
       <c r="G118" t="n">
-        <v>1795.76</v>
+        <v>11860.16</v>
       </c>
       <c r="H118" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
-          <t>WM-SP-POS stand- Multi - PT</t>
+          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - Phrase</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>B0FN4FPJ83</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>10.04</v>
+        <v>2509.5</v>
       </c>
       <c r="E119" t="n">
-        <v>1</v>
+        <v>122</v>
       </c>
       <c r="F119" t="n">
-        <v>18</v>
+        <v>8880</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>8911.870000000001</v>
       </c>
       <c r="H119" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
+          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 -Phrase</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>B0FN4D3C89</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0</v>
+        <v>2755.64</v>
       </c>
       <c r="E120" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="F120" t="n">
-        <v>0</v>
+        <v>27077</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>1795.76</v>
       </c>
       <c r="H120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
+          <t>WM-SP-POS stand- Multi - PT</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>B0FN4DSQ6P</t>
+          <t>B0FN4FPJ83</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1042.42</v>
+        <v>10.04</v>
       </c>
       <c r="E121" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="F121" t="n">
-        <v>8951</v>
+        <v>18</v>
       </c>
       <c r="G121" t="n">
-        <v>2326.28</v>
+        <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -3829,17 +3829,17 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>B0FN4HDM6Z</t>
+          <t>B0FN4D3C89</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>598.99</v>
+        <v>0</v>
       </c>
       <c r="E122" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>3460</v>
+        <v>0</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3852,56 +3852,56 @@
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
+          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>B0FHVWHQHR</t>
+          <t>B0FN4DSQ6P</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>6.68</v>
+        <v>1042.42</v>
       </c>
       <c r="E123" t="n">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="F123" t="n">
-        <v>864</v>
+        <v>8951</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>2326.28</v>
       </c>
       <c r="H123" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
+          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>B0FN4D3C89</t>
+          <t>B0FN4HDM6Z</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>449.69</v>
+        <v>598.99</v>
       </c>
       <c r="E124" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="F124" t="n">
-        <v>8638</v>
+        <v>3460</v>
       </c>
       <c r="G124" t="n">
-        <v>1835.6</v>
+        <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -3913,17 +3913,17 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>B0FN4DSQ6P</t>
+          <t>B0FHVWHQHR</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>106.69</v>
+        <v>6.68</v>
       </c>
       <c r="E125" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F125" t="n">
-        <v>5077</v>
+        <v>864</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3936,56 +3936,56 @@
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>B0FHVWHQHR</t>
+          <t>B0FN4D3C89</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>68.55</v>
+        <v>449.69</v>
       </c>
       <c r="E126" t="n">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="F126" t="n">
-        <v>1985</v>
+        <v>8638</v>
       </c>
       <c r="G126" t="n">
-        <v>490.68</v>
+        <v>1835.6</v>
       </c>
       <c r="H126" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>B0FN4D3C89</t>
+          <t>B0FN4DSQ6P</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>303.75</v>
+        <v>106.69</v>
       </c>
       <c r="E127" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F127" t="n">
-        <v>1920</v>
+        <v>5077</v>
       </c>
       <c r="G127" t="n">
-        <v>727.12</v>
+        <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -3997,23 +3997,23 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>B0FN4DSQ6P</t>
+          <t>B0FHVWHQHR</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1056.31</v>
+        <v>68.55</v>
       </c>
       <c r="E128" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="F128" t="n">
-        <v>3315</v>
+        <v>1985</v>
       </c>
       <c r="G128" t="n">
-        <v>3434.76</v>
+        <v>490.68</v>
       </c>
       <c r="H128" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
@@ -4025,157 +4025,157 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>B0FN4HDM6Z</t>
+          <t>B0FN4D3C89</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>636.1899999999999</v>
+        <v>303.75</v>
       </c>
       <c r="E129" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F129" t="n">
-        <v>1033</v>
+        <v>1920</v>
       </c>
       <c r="G129" t="n">
-        <v>1778.81</v>
+        <v>727.12</v>
       </c>
       <c r="H129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
+          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>B0FN4D3C89</t>
+          <t>B0FN4DSQ6P</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>563.4300000000001</v>
+        <v>1056.31</v>
       </c>
       <c r="E130" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="F130" t="n">
-        <v>6152</v>
+        <v>3315</v>
       </c>
       <c r="G130" t="n">
-        <v>2727.12</v>
+        <v>3434.76</v>
       </c>
       <c r="H130" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
+          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>B0FN4DSQ6P</t>
+          <t>B0FN4HDM6Z</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>613.12</v>
+        <v>636.1899999999999</v>
       </c>
       <c r="E131" t="n">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="F131" t="n">
-        <v>10704</v>
+        <v>1033</v>
       </c>
       <c r="G131" t="n">
-        <v>6996.639999999999</v>
+        <v>1778.81</v>
       </c>
       <c r="H131" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
-          <t>WM_SP_KT_Adjustable_Exact_Manual_HV</t>
+          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0FN4D3C89</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>3286.29</v>
+        <v>563.4300000000001</v>
       </c>
       <c r="E132" t="n">
-        <v>131</v>
+        <v>50</v>
       </c>
       <c r="F132" t="n">
-        <v>89428</v>
+        <v>6152</v>
       </c>
       <c r="G132" t="n">
-        <v>12712.71</v>
+        <v>2727.12</v>
       </c>
       <c r="H132" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr">
         <is>
-          <t>White Mulberry-Motorized-SP-KT-BM</t>
+          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0FN4DSQ6P</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1221.24</v>
+        <v>613.12</v>
       </c>
       <c r="E133" t="n">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="F133" t="n">
-        <v>13109</v>
+        <v>10704</v>
       </c>
       <c r="G133" t="n">
-        <v>12712.71</v>
+        <v>6996.639999999999</v>
       </c>
       <c r="H133" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
-          <t>White Mulberry-Motorized-SP-KT-BM</t>
+          <t>WM_SP_KT_Adjustable_Exact_Manual_HV</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>625.12</v>
+        <v>3286.29</v>
       </c>
       <c r="E134" t="n">
-        <v>33</v>
+        <v>131</v>
       </c>
       <c r="F134" t="n">
-        <v>10232</v>
+        <v>89428</v>
       </c>
       <c r="G134" t="n">
         <v>12712.71</v>
@@ -4539,7 +4539,7 @@
         <v>77</v>
       </c>
       <c r="F11" t="n">
-        <v>25300</v>
+        <v>25298</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -4623,7 +4623,7 @@
         <v>95</v>
       </c>
       <c r="F14" t="n">
-        <v>45409</v>
+        <v>45404</v>
       </c>
       <c r="G14" t="n">
         <v>2783.9</v>
@@ -4651,7 +4651,7 @@
         <v>72</v>
       </c>
       <c r="F15" t="n">
-        <v>21755</v>
+        <v>21754</v>
       </c>
       <c r="G15" t="n">
         <v>2626.27</v>
@@ -4755,7 +4755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5214,19 +5214,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3617</v>
+        <v>7316</v>
       </c>
       <c r="E14" t="n">
-        <v>147</v>
+        <v>298</v>
       </c>
       <c r="F14" t="n">
-        <v>342.3705162078417</v>
+        <v>692.4299999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>19440.3836331897</v>
+        <v>39317.36</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -5243,23 +5243,23 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1809</v>
+        <v>7316</v>
       </c>
       <c r="E15" t="n">
-        <v>74</v>
+        <v>298</v>
       </c>
       <c r="F15" t="n">
-        <v>171.1852581039208</v>
+        <v>692.4299999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>9720.191816594852</v>
+        <v>39317.36</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -5271,28 +5271,28 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
+          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>9205</v>
+        <v>3682</v>
       </c>
       <c r="E16" t="n">
-        <v>375</v>
+        <v>62</v>
       </c>
       <c r="F16" t="n">
-        <v>871.3042256882374</v>
+        <v>487.7133333333334</v>
       </c>
       <c r="G16" t="n">
-        <v>49474.14455021545</v>
+        <v>10875.98666666667</v>
       </c>
       <c r="H16" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -5309,23 +5309,23 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0DQ1NV8D2</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11047</v>
+        <v>3682</v>
       </c>
       <c r="E17" t="n">
-        <v>187</v>
+        <v>62</v>
       </c>
       <c r="F17" t="n">
-        <v>1463.14</v>
+        <v>487.7133333333334</v>
       </c>
       <c r="G17" t="n">
-        <v>32627.96</v>
+        <v>10875.98666666667</v>
       </c>
       <c r="H17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -5337,25 +5337,25 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SB-Lshape-Multi Asin- KT- phrase</t>
+          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1560</v>
+        <v>3682</v>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="F18" t="n">
-        <v>257.44</v>
+        <v>487.7133333333334</v>
       </c>
       <c r="G18" t="n">
-        <v>7075.42</v>
+        <v>10875.98666666667</v>
       </c>
       <c r="H18" t="n">
         <v>1</v>
@@ -5370,28 +5370,28 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
+          <t>SB-Lshape-Multi Asin- KT- phrase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>9999</v>
+        <v>390</v>
       </c>
       <c r="E19" t="n">
-        <v>105</v>
+        <v>13</v>
       </c>
       <c r="F19" t="n">
-        <v>1265.03</v>
+        <v>64.36</v>
       </c>
       <c r="G19" t="n">
-        <v>5252.54</v>
+        <v>1768.855</v>
       </c>
       <c r="H19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -5403,28 +5403,28 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
+          <t>SB-Lshape-Multi Asin- KT- phrase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0BFVNS8HS</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>19414</v>
+        <v>390</v>
       </c>
       <c r="E20" t="n">
-        <v>202</v>
+        <v>13</v>
       </c>
       <c r="F20" t="n">
-        <v>2717.31</v>
+        <v>64.36</v>
       </c>
       <c r="G20" t="n">
-        <v>5579.66</v>
+        <v>1768.855</v>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -5436,25 +5436,25 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>SB-Lshape-Multi Asin- KT- phrase</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>390</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F21" t="n">
-        <v>4.718333333333333</v>
+        <v>64.36</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1768.855</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -5469,25 +5469,25 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>SB-Lshape-Multi Asin- KT- phrase</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>7</v>
+        <v>390</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F22" t="n">
-        <v>4.718333333333333</v>
+        <v>64.36</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1768.855</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -5502,28 +5502,28 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>9999</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>105</v>
       </c>
       <c r="F23" t="n">
-        <v>4.718333333333333</v>
+        <v>1265.03</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>5252.54</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -5535,28 +5535,28 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>7</v>
+        <v>19414</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>202</v>
       </c>
       <c r="F24" t="n">
-        <v>4.718333333333333</v>
+        <v>2717.31</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>5579.66</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -5573,7 +5573,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -5634,28 +5634,28 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Defensive</t>
+          <t>WM-SB-Monitor Arms-Branded</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3803</v>
+        <v>7</v>
       </c>
       <c r="E27" t="n">
-        <v>57</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>613.13</v>
+        <v>4.718333333333333</v>
       </c>
       <c r="G27" t="n">
-        <v>2329.66</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -5667,30 +5667,162 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>B0DB5YTQZV</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>7</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4.718333333333333</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>B0DP2Z5DQ9</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>7</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4.718333333333333</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>7</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>4.718333333333333</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Defensive</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>3803</v>
+      </c>
+      <c r="E31" t="n">
+        <v>57</v>
+      </c>
+      <c r="F31" t="n">
+        <v>613.13</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2329.66</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>B0DB5VG39T</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D32" t="n">
         <v>17299</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E32" t="n">
         <v>140</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F32" t="n">
         <v>2415.43</v>
       </c>
-      <c r="G28" t="n">
-        <v>4659.32</v>
-      </c>
-      <c r="H28" t="n">
-        <v>3</v>
-      </c>
-      <c r="I28" t="inlineStr">
+      <c r="G32" t="n">
+        <v>6988.98</v>
+      </c>
+      <c r="H32" t="n">
+        <v>4</v>
+      </c>
+      <c r="I32" t="inlineStr">
         <is>
           <t>White Mulberry</t>
         </is>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week23.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week23.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H135"/>
+  <dimension ref="A1:H128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,7 +563,7 @@
         <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>468.1799999999999</v>
+        <v>137.29</v>
       </c>
       <c r="E6" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>2489</v>
+        <v>708</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -613,13 +613,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>98.94999999999999</v>
+        <v>53.08</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>1823</v>
+        <v>483</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -641,13 +641,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1556.51</v>
+        <v>1265.92</v>
       </c>
       <c r="E8" t="n">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="F8" t="n">
-        <v>13616</v>
+        <v>11818</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -669,19 +669,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2003.88</v>
+        <v>1671.8</v>
       </c>
       <c r="E9" t="n">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="F9" t="n">
-        <v>20565</v>
+        <v>17110</v>
       </c>
       <c r="G9" t="n">
-        <v>7117.8</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -697,13 +697,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1816.54</v>
+        <v>1529.83</v>
       </c>
       <c r="E10" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F10" t="n">
-        <v>3932</v>
+        <v>3123</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>883.8099999999999</v>
+        <v>614.8</v>
       </c>
       <c r="E11" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F11" t="n">
-        <v>3935</v>
+        <v>3199</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>496.21</v>
+        <v>403.5</v>
       </c>
       <c r="E12" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F12" t="n">
-        <v>6045</v>
+        <v>4895</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -781,13 +781,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1030.08</v>
+        <v>729.0999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="F13" t="n">
-        <v>8425</v>
+        <v>7588</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -815,7 +815,7 @@
         <v>13</v>
       </c>
       <c r="F14" t="n">
-        <v>7221</v>
+        <v>7074</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -837,13 +837,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>796.27</v>
+        <v>730.1500000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F15" t="n">
-        <v>2198</v>
+        <v>2094</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -871,7 +871,7 @@
         <v>13</v>
       </c>
       <c r="F16" t="n">
-        <v>3235</v>
+        <v>3175</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1037.09</v>
+        <v>676</v>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="F17" t="n">
-        <v>11353</v>
+        <v>7679</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -921,13 +921,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>383.01</v>
+        <v>278.79</v>
       </c>
       <c r="E18" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F18" t="n">
-        <v>9135</v>
+        <v>6320</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1011,7 +1011,7 @@
         <v>20</v>
       </c>
       <c r="F21" t="n">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1039,7 +1039,7 @@
         <v>21</v>
       </c>
       <c r="F22" t="n">
-        <v>3361</v>
+        <v>3360</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1067,7 +1067,7 @@
         <v>75</v>
       </c>
       <c r="F23" t="n">
-        <v>13108</v>
+        <v>13107</v>
       </c>
       <c r="G23" t="n">
         <v>12712.71</v>
@@ -1151,7 +1151,7 @@
         <v>33</v>
       </c>
       <c r="F26" t="n">
-        <v>18298</v>
+        <v>18297</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1235,7 +1235,7 @@
         <v>2</v>
       </c>
       <c r="F29" t="n">
-        <v>596</v>
+        <v>543</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1257,13 +1257,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>312.17</v>
+        <v>248.8</v>
       </c>
       <c r="E30" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F30" t="n">
-        <v>7609</v>
+        <v>7244</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1291,7 +1291,7 @@
         <v>18</v>
       </c>
       <c r="F31" t="n">
-        <v>1991</v>
+        <v>1916</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
         <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>2659</v>
+        <v>2100</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1347,7 +1347,7 @@
         <v>7</v>
       </c>
       <c r="F33" t="n">
-        <v>1518</v>
+        <v>1448</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1375,7 +1375,7 @@
         <v>19</v>
       </c>
       <c r="F34" t="n">
-        <v>6342</v>
+        <v>6266</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1397,13 +1397,13 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>852.89</v>
+        <v>781.35</v>
       </c>
       <c r="E35" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F35" t="n">
-        <v>6393</v>
+        <v>5875</v>
       </c>
       <c r="G35" t="n">
         <v>22032.2</v>
@@ -1425,13 +1425,13 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>124.91</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F36" t="n">
-        <v>1492</v>
+        <v>1142</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1453,13 +1453,13 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>3389.71</v>
+        <v>2782.58</v>
       </c>
       <c r="E37" t="n">
-        <v>146</v>
+        <v>120</v>
       </c>
       <c r="F37" t="n">
-        <v>25285</v>
+        <v>21496</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1481,13 +1481,13 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1052.21</v>
+        <v>780.47</v>
       </c>
       <c r="E38" t="n">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="F38" t="n">
-        <v>12849</v>
+        <v>9093</v>
       </c>
       <c r="G38" t="n">
         <v>49782.18</v>
@@ -1509,13 +1509,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1298.48</v>
+        <v>1110.16</v>
       </c>
       <c r="E39" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F39" t="n">
-        <v>5566</v>
+        <v>4692</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1528,7 +1528,7 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multi Asin- AT</t>
+          <t>Camb-SP-Lshape-Multiple Asins- Exact 01</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1537,41 +1537,41 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>263.02</v>
+        <v>2756.27</v>
       </c>
       <c r="E40" t="n">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="F40" t="n">
-        <v>960</v>
+        <v>36848</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>13105.08</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multi Asin- AT</t>
+          <t>Camb-SP-Lshape-Multiple Asins- Exact 01</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B0BFVNS8HS</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>247.18</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F41" t="n">
-        <v>40</v>
+        <v>4637</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1584,22 +1584,22 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multi Asin- AT</t>
+          <t>Camb-SP-Lshape-Multiple Asins- Exact/Phrase</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>89.8</v>
+        <v>281.29</v>
       </c>
       <c r="E42" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="F42" t="n">
-        <v>1095</v>
+        <v>2679</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1612,78 +1612,78 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multi Asin- AT</t>
+          <t>Camb-SP-Lshape-Multiple Asins- Exact/Phrase</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>93.31999999999999</v>
+        <v>2062.61</v>
       </c>
       <c r="E43" t="n">
-        <v>4</v>
+        <v>90</v>
       </c>
       <c r="F43" t="n">
-        <v>1171</v>
+        <v>28768</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>7075.42</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multiple Asins- Exact 01</t>
+          <t>Camb-SP-Lshape-Multiple Asins- Exact/Phrase</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>3157.18</v>
+        <v>463.48</v>
       </c>
       <c r="E44" t="n">
-        <v>149</v>
+        <v>21</v>
       </c>
       <c r="F44" t="n">
-        <v>40735</v>
+        <v>7636</v>
       </c>
       <c r="G44" t="n">
-        <v>13105.08</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multiple Asins- Exact 01</t>
+          <t>Camb-SP-Motorized Desk- B0CPT3Q25C- Exact</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>462.51</v>
+        <v>713.9400000000001</v>
       </c>
       <c r="E45" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F45" t="n">
-        <v>6918</v>
+        <v>4448</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1696,22 +1696,22 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multiple Asins- Exact/Phrase</t>
+          <t>Camb-SP-Motorized Desk-B0CPT3Q25C - PT01</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>358.74</v>
+        <v>2084.73</v>
       </c>
       <c r="E46" t="n">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="F46" t="n">
-        <v>3551</v>
+        <v>10629</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1724,78 +1724,78 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multiple Asins- Exact/Phrase</t>
+          <t>Camb-SP-Motorized Desk-B0CPT3Q25C- Exact</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2471.67</v>
+        <v>1074.29</v>
       </c>
       <c r="E47" t="n">
-        <v>110</v>
+        <v>36</v>
       </c>
       <c r="F47" t="n">
-        <v>35498</v>
+        <v>9600</v>
       </c>
       <c r="G47" t="n">
-        <v>7075.42</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multiple Asins- Exact/Phrase</t>
+          <t>Camb-SP-Zshape-B0CPFS24ML- CT ref</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>505.04</v>
+        <v>2233.12</v>
       </c>
       <c r="E48" t="n">
-        <v>24</v>
+        <v>122</v>
       </c>
       <c r="F48" t="n">
-        <v>8530</v>
+        <v>19956</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>21607.62</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Camb-SP-Motorized Desk- B0CPT3Q25C- Exact</t>
+          <t>Camb-SP-Zshape-B0CPFS24ML- PT</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1036.11</v>
+        <v>2463.34</v>
       </c>
       <c r="E49" t="n">
-        <v>27</v>
+        <v>162</v>
       </c>
       <c r="F49" t="n">
-        <v>8965</v>
+        <v>11794</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1808,91 +1808,91 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Camb-SP-Motorized Desk-B0CPT3Q25C - PT01</t>
+          <t>Camb-SP-Zshape-B0CPFS24ML- Phrase</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2398.7</v>
+        <v>2402.84</v>
       </c>
       <c r="E50" t="n">
-        <v>103</v>
+        <v>185</v>
       </c>
       <c r="F50" t="n">
-        <v>12424</v>
+        <v>25981</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>7202.54</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Camb-SP-Motorized Desk-B0CPT3Q25C- Exact</t>
+          <t>Camb-SP-Zshape-B0CPFS24ML-PT01</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1717.93</v>
+        <v>1614.22</v>
       </c>
       <c r="E51" t="n">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="F51" t="n">
-        <v>16286</v>
+        <v>5150</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>11016.1</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Camb-SP-Zshape-B0CPFS24ML- CT ref</t>
+          <t>Camb-SP-stand desk- B0DQ1NV8D2- PT</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2632.43</v>
+        <v>1542.36</v>
       </c>
       <c r="E52" t="n">
-        <v>147</v>
+        <v>43</v>
       </c>
       <c r="F52" t="n">
-        <v>21973</v>
+        <v>5430</v>
       </c>
       <c r="G52" t="n">
-        <v>21607.62</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Camb-SP-Zshape-B0CPFS24ML- PT</t>
+          <t>Camb-Zshape-Gaming- B0CPFS24ML-Phrase/Exact</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1901,26 +1901,26 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>3018.27</v>
+        <v>3086.02</v>
       </c>
       <c r="E53" t="n">
-        <v>198</v>
+        <v>296</v>
       </c>
       <c r="F53" t="n">
-        <v>14498</v>
+        <v>40112</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>7202.54</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Camb-SP-Zshape-B0CPFS24ML- Phrase</t>
+          <t>SP CT PT_B0CPFS24ML_Gaming</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1929,13 +1929,13 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2734.84</v>
+        <v>2217.23</v>
       </c>
       <c r="E54" t="n">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="F54" t="n">
-        <v>30513</v>
+        <v>16886</v>
       </c>
       <c r="G54" t="n">
         <v>7202.54</v>
@@ -1948,7 +1948,7 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Camb-SP-Zshape-B0CPFS24ML-PT01</t>
+          <t>SP KT_B0CPFS24ML_Manual_Gaming</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1957,41 +1957,41 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1867.73</v>
+        <v>718.3699999999999</v>
       </c>
       <c r="E55" t="n">
-        <v>97</v>
+        <v>44</v>
       </c>
       <c r="F55" t="n">
-        <v>6225</v>
+        <v>3510</v>
       </c>
       <c r="G55" t="n">
-        <v>11016.1</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Camb-SP-stand desk- B0DQ1NV8D2- PT</t>
+          <t>SP_KT_L shape Non Performing Ex</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1826.2</v>
+        <v>173.93</v>
       </c>
       <c r="E56" t="n">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="F56" t="n">
-        <v>6032</v>
+        <v>1907</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -2004,78 +2004,78 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Camb-Zshape-Gaming- B0CPFS24ML-Phrase/Exact</t>
+          <t>SP_KT_L shape Non Performing Ex</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3603.81</v>
+        <v>210.5</v>
       </c>
       <c r="E57" t="n">
-        <v>347</v>
+        <v>11</v>
       </c>
       <c r="F57" t="n">
-        <v>45882</v>
+        <v>2043</v>
       </c>
       <c r="G57" t="n">
-        <v>14405.08</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SP CT PT_B0CPFS24ML_Gaming</t>
+          <t>SP_KT_L shape Non Performing Ex</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>2526.64</v>
+        <v>214.35</v>
       </c>
       <c r="E58" t="n">
-        <v>246</v>
+        <v>12</v>
       </c>
       <c r="F58" t="n">
-        <v>19140</v>
+        <v>3734</v>
       </c>
       <c r="G58" t="n">
-        <v>14405.08</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SP KT_B0CPFS24ML_Manual_Gaming</t>
+          <t>SP_PT_L shape Non Performing PT</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1154.3</v>
+        <v>824.74</v>
       </c>
       <c r="E59" t="n">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="F59" t="n">
-        <v>5915</v>
+        <v>2621</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -2088,22 +2088,22 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SP_KT_L shape Non Performing Ex</t>
+          <t>SP_PT_L shape Non Performing PT</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>185.02</v>
+        <v>756.84</v>
       </c>
       <c r="E60" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F60" t="n">
-        <v>2635</v>
+        <v>5556</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2116,22 +2116,22 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SP_KT_L shape Non Performing Ex</t>
+          <t>WB- SP- B0DB5VG39T - PT</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>231.9</v>
+        <v>1544.27</v>
       </c>
       <c r="E61" t="n">
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="F61" t="n">
-        <v>3142</v>
+        <v>9061</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2144,22 +2144,22 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SP_KT_L shape Non Performing Ex</t>
+          <t>WB- SP- B0DB5YTQZV-B0DB5VVPSB- PT</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>228.14</v>
+        <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>4240</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2172,22 +2172,22 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SP_PT_L shape Non Performing PT</t>
+          <t>WB- SP- B0DP2VVRND - PT</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0DP2VVRND</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>993.91</v>
+        <v>249.31</v>
       </c>
       <c r="E63" t="n">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="F63" t="n">
-        <v>3097</v>
+        <v>439</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2200,22 +2200,22 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SP_PT_L shape Non Performing PT</t>
+          <t>WB- SP- B0DP2WC5VW - PT</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>841.9100000000001</v>
+        <v>60.42</v>
       </c>
       <c r="E64" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
-        <v>6758</v>
+        <v>102</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2228,50 +2228,50 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>WB- SP- B0DB5VG39T - PT</t>
+          <t>WB- SP- B0DP32F346 - PT</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1811.25</v>
+        <v>1776.29</v>
       </c>
       <c r="E65" t="n">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="F65" t="n">
-        <v>10838</v>
+        <v>4870</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>2626.27</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>WB- SP- B0DB5YTQZV-B0DB5VVPSB- PT</t>
+          <t>WM- Adj Metal desk- B0DB5W4TCP-SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>24.71</v>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>712</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2284,12 +2284,12 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>WB- SP- B0DB5YTQZV-B0DB5VVPSB- PT</t>
+          <t>WM- Height Adj stand - B0DP2VVRND-SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP2VVRND</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2312,96 +2312,96 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>WB- SP- B0DP2VVRND - PT</t>
+          <t>WM- Height Adj stand Dual-B0DB5YTQZV-SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>B0DP2VVRND</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>249.31</v>
+        <v>2691.57</v>
       </c>
       <c r="E68" t="n">
-        <v>16</v>
+        <v>123</v>
       </c>
       <c r="F68" t="n">
-        <v>440</v>
+        <v>17812</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>3388.14</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>WB- SP- B0DP2WC5VW - PT</t>
+          <t>WM- Height Adjustable stand- Dual-B0DB5YTQZV- PT</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>175.15</v>
+        <v>1847.43</v>
       </c>
       <c r="E69" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="F69" t="n">
-        <v>264</v>
+        <v>2830</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>9736.440000000001</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>WB- SP- B0DP32F346 - PT</t>
+          <t>WM- SP- Adj Metal desk- Multi Asins- PT</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>2040.75</v>
+        <v>754.13</v>
       </c>
       <c r="E70" t="n">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="F70" t="n">
-        <v>6587</v>
+        <v>6475</v>
       </c>
       <c r="G70" t="n">
-        <v>2626.27</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>WB- SP-B0DB5W4TCP-PT</t>
+          <t>WM- SP- Adj Metal desk- Multi Asins- PT</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2424,22 +2424,22 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>WM- Adj Metal desk- B0DB5W4TCP-SP-KT-Phrase</t>
+          <t>WM- SP- Height Adjustable stand- Dual-B0DB5YTQZV- Broad</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>394.12</v>
+        <v>726.63</v>
       </c>
       <c r="E72" t="n">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="F72" t="n">
-        <v>2208</v>
+        <v>9934</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2452,22 +2452,22 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>WM- Height Adj stand - B0DP2VVRND-SP-KT-Phrase</t>
+          <t>WM- SP- Wall Mounted Stand- B0DP2WC5VW- Broad</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>B0DP2VVRND</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
+        <v>196.57</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>1984</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2480,134 +2480,134 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>WM- Height Adj stand Dual-B0DB5YTQZV-SP-KT-Phrase/BM</t>
+          <t>WM- SP- Wooden Arm- B0DP32F346- PT</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>3059.83</v>
+        <v>2239.73</v>
       </c>
       <c r="E74" t="n">
-        <v>139</v>
+        <v>72</v>
       </c>
       <c r="F74" t="n">
-        <v>19930</v>
+        <v>14485</v>
       </c>
       <c r="G74" t="n">
-        <v>3388.14</v>
+        <v>12934.37</v>
       </c>
       <c r="H74" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>WM- Height Adjustable stand- Dual-B0DB5YTQZV- PT</t>
+          <t>WM- SP-Wall Mounted Stand- B0DP2WC5VW- Exact &amp; Phrase</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>2202.9</v>
+        <v>769.54</v>
       </c>
       <c r="E75" t="n">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="F75" t="n">
-        <v>3251</v>
+        <v>2000</v>
       </c>
       <c r="G75" t="n">
-        <v>10829.66</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>WM- SP- Adj Metal desk- Multi Asins- PT</t>
+          <t>WM- Wall Mounted Stand- B0DP2WC5VW- PT</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1021.35</v>
+        <v>634.08</v>
       </c>
       <c r="E76" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="F76" t="n">
-        <v>7617</v>
+        <v>2001</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>5579.66</v>
       </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>WM- SP- Adj Metal desk- Multi Asins- PT</t>
+          <t>WM- Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
+        <v>1280.61</v>
       </c>
       <c r="E77" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>7989</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>2783.9</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>WM- SP- Height Adjustable stand- Dual-B0DB5YTQZV- Broad</t>
+          <t>WM- Wall Mounted Stand- B0DP2WC5VW- SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>941.77</v>
+        <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>11633</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2620,25 +2620,25 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>WM- SP- Wall Mounted Stand- B0DP2WC5VW- Broad</t>
+          <t>WM-Gas Spring MA- B0DB5VG39T-SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>444.67</v>
+        <v>2227.44</v>
       </c>
       <c r="E79" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F79" t="n">
-        <v>3484</v>
+        <v>9613</v>
       </c>
       <c r="G79" t="n">
-        <v>2795.76</v>
+        <v>2329.66</v>
       </c>
       <c r="H79" t="n">
         <v>1</v>
@@ -2648,50 +2648,50 @@
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>WM- SP- Wooden Arm- B0DP32F346- PT</t>
+          <t>WM-Gas Spring MA- Dual - B0DB5VVPSB-SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>2608.73</v>
+        <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>16332</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>12934.37</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>WM- SP-Wall Mounted Stand- B0DP2WC5VW- Exact &amp; Phrase</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1156.38</v>
+        <v>1078.08</v>
       </c>
       <c r="E81" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F81" t="n">
-        <v>2912</v>
+        <v>7068</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2704,7 +2704,7 @@
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>WM- Wall Mounted Stand- B0DP2WC5VW- PT</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2713,69 +2713,69 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>859.1600000000001</v>
+        <v>390.2</v>
       </c>
       <c r="E82" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F82" t="n">
-        <v>2540</v>
+        <v>8845</v>
       </c>
       <c r="G82" t="n">
-        <v>8375.42</v>
+        <v>2965.25</v>
       </c>
       <c r="H82" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>WM- Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1959.49</v>
+        <v>615.21</v>
       </c>
       <c r="E83" t="n">
-        <v>93</v>
+        <v>34</v>
       </c>
       <c r="F83" t="n">
-        <v>10655</v>
+        <v>15277</v>
       </c>
       <c r="G83" t="n">
-        <v>8375.42</v>
+        <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>WM- Wall Mounted Stand- B0DP2WC5VW- SP-KT-Phrase/BM</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>445</v>
       </c>
       <c r="E84" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>17190</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2788,134 +2788,134 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>WM-Gas Spring MA- B0DB5VG39T-SP-KT-Phrase/BM</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>2534.24</v>
+        <v>480.74</v>
       </c>
       <c r="E85" t="n">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="F85" t="n">
-        <v>11393</v>
+        <v>3864</v>
       </c>
       <c r="G85" t="n">
-        <v>2329.66</v>
+        <v>2932.2</v>
       </c>
       <c r="H85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>WM-Gas Spring MA- Dual - B0DB5VVPSB-SP-KT-Phrase/BM</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>762.73</v>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>4153</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>2783.9</v>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1135.44</v>
+        <v>1063.72</v>
       </c>
       <c r="E87" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F87" t="n">
-        <v>7833</v>
+        <v>6962</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>5155.93</v>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>565.67</v>
+        <v>204.02</v>
       </c>
       <c r="E88" t="n">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="F88" t="n">
-        <v>12969</v>
+        <v>2090</v>
       </c>
       <c r="G88" t="n">
-        <v>2965.25</v>
+        <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - exact</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>653.38</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>16094</v>
+        <v>0</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2928,22 +2928,22 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - exact</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>534.4300000000001</v>
+        <v>583.29</v>
       </c>
       <c r="E90" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F90" t="n">
-        <v>19329</v>
+        <v>11749</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2956,124 +2956,124 @@
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
+          <t>WM-SP- Premium Monitor Arms- Multi Asins -Phrase</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>517.61</v>
+        <v>2188.92</v>
       </c>
       <c r="E91" t="n">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="F91" t="n">
-        <v>4120</v>
+        <v>20773</v>
       </c>
       <c r="G91" t="n">
-        <v>2932.2</v>
+        <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
+          <t>WM-SP-Gas Spring -Multi Asins- Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1014.82</v>
+        <v>2173.21</v>
       </c>
       <c r="E92" t="n">
-        <v>50</v>
+        <v>96</v>
       </c>
       <c r="F92" t="n">
-        <v>5140</v>
+        <v>45547</v>
       </c>
       <c r="G92" t="n">
-        <v>2783.9</v>
+        <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
+          <t>WM-SP-Gas Spring -Multi Asins- Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1102.53</v>
+        <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>7319</v>
+        <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>5155.93</v>
+        <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T- Broad</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>229.8</v>
+        <v>1810.99</v>
       </c>
       <c r="E94" t="n">
-        <v>14</v>
+        <v>116</v>
       </c>
       <c r="F94" t="n">
-        <v>2225</v>
+        <v>20465</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>8036.46</v>
       </c>
       <c r="H94" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - exact</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T- Exact &amp; Phrase</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3096,91 +3096,91 @@
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - exact</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>859.26</v>
+        <v>1215.77</v>
       </c>
       <c r="E96" t="n">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F96" t="n">
-        <v>17572</v>
+        <v>1872</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>6141.52</v>
       </c>
       <c r="H96" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>WM-SP- Premium Monitor Arms- Multi Asins -Phrase</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>B0DP3194QN</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>781.22</v>
       </c>
       <c r="E97" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>2265</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>4151.69</v>
       </c>
       <c r="H97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>WM-SP- Premium Monitor Arms- Multi Asins -Phrase</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>2452.04</v>
+        <v>134.76</v>
       </c>
       <c r="E98" t="n">
-        <v>96</v>
+        <v>5</v>
       </c>
       <c r="F98" t="n">
-        <v>22495</v>
+        <v>691</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>2372.03</v>
       </c>
       <c r="H98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring -Multi Asins- Phrase &amp; Exact</t>
+          <t>WM-SP-Monitor Arms- Branded</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3189,26 +3189,26 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>2528.17</v>
+        <v>556.29</v>
       </c>
       <c r="E99" t="n">
-        <v>112</v>
+        <v>33</v>
       </c>
       <c r="F99" t="n">
-        <v>51447</v>
+        <v>7059</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>2329.66</v>
       </c>
       <c r="H99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring -Multi Asins- Phrase &amp; Exact</t>
+          <t>WM-SP-Monitor Arms- Branded</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3217,13 +3217,13 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0</v>
+        <v>152.9</v>
       </c>
       <c r="E100" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>1499</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3236,50 +3236,50 @@
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T- Broad</t>
+          <t>WM-SP-Monitor Arms- Branded</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>2147.19</v>
+        <v>190.43</v>
       </c>
       <c r="E101" t="n">
-        <v>146</v>
+        <v>10</v>
       </c>
       <c r="F101" t="n">
-        <v>26343</v>
+        <v>2383</v>
       </c>
       <c r="G101" t="n">
-        <v>15025.44</v>
+        <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T- Exact &amp; Phrase</t>
+          <t>WM-SP-Monitor Arms- Branded</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
+        <v>68.81</v>
       </c>
       <c r="E102" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F102" t="n">
-        <v>0</v>
+        <v>1737</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3292,134 +3292,134 @@
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
+          <t>WM-SP-Monitor Arms- Branded</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1556.37</v>
+        <v>179.89</v>
       </c>
       <c r="E103" t="n">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="F103" t="n">
-        <v>2409</v>
+        <v>4346</v>
       </c>
       <c r="G103" t="n">
-        <v>6141.52</v>
+        <v>7202.54</v>
       </c>
       <c r="H103" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
+          <t>WM-SP-Monitor Arms- Branded</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>852.29</v>
+        <v>173.56</v>
       </c>
       <c r="E104" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F104" t="n">
-        <v>2473</v>
+        <v>3755</v>
       </c>
       <c r="G104" t="n">
-        <v>4151.69</v>
+        <v>7944.92</v>
       </c>
       <c r="H104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
+          <t>WM-SP-Monitor Arms- Defensive</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>134.76</v>
+        <v>146.64</v>
       </c>
       <c r="E105" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F105" t="n">
-        <v>691</v>
+        <v>977</v>
       </c>
       <c r="G105" t="n">
-        <v>2372.03</v>
+        <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Branded</t>
+          <t>WM-SP-Monitor Arms- Defensive</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>586.49</v>
+        <v>207.95</v>
       </c>
       <c r="E106" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="F106" t="n">
-        <v>7351</v>
+        <v>2768</v>
       </c>
       <c r="G106" t="n">
-        <v>2329.66</v>
+        <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Branded</t>
+          <t>WM-SP-Monitor Arms- Defensive</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>176.9</v>
+        <v>125.99</v>
       </c>
       <c r="E107" t="n">
         <v>10</v>
       </c>
       <c r="F107" t="n">
-        <v>1660</v>
+        <v>1106</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3432,81 +3432,81 @@
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Branded</t>
+          <t>WM-SP-Monitor Arms- Defensive</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>206.6</v>
+        <v>410.9</v>
       </c>
       <c r="E108" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F108" t="n">
-        <v>2753</v>
+        <v>4822</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>1694.07</v>
       </c>
       <c r="H108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Branded</t>
+          <t>WM-SP-Monitor Arms- Defensive</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>86.90000000000001</v>
+        <v>503</v>
       </c>
       <c r="E109" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="F109" t="n">
-        <v>1936</v>
+        <v>5245</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>4744.07</v>
       </c>
       <c r="H109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Branded</t>
+          <t>WM-SP-Monitor Arms- Defensive</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>254.5</v>
+        <v>62.8</v>
       </c>
       <c r="E110" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F110" t="n">
-        <v>5163</v>
+        <v>796</v>
       </c>
       <c r="G110" t="n">
-        <v>7202.54</v>
+        <v>2626.27</v>
       </c>
       <c r="H110" t="n">
         <v>1</v>
@@ -3516,106 +3516,106 @@
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Branded</t>
+          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - PT</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>173.56</v>
+        <v>1304.17</v>
       </c>
       <c r="E111" t="n">
-        <v>12</v>
+        <v>85</v>
       </c>
       <c r="F111" t="n">
-        <v>4431</v>
+        <v>6166</v>
       </c>
       <c r="G111" t="n">
-        <v>7944.92</v>
+        <v>11860.16</v>
       </c>
       <c r="H111" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Defensive</t>
+          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - Phrase</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>161.18</v>
+        <v>2244.5</v>
       </c>
       <c r="E112" t="n">
-        <v>12</v>
+        <v>110</v>
       </c>
       <c r="F112" t="n">
-        <v>1131</v>
+        <v>8185</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>8911.870000000001</v>
       </c>
       <c r="H112" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Defensive</t>
+          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 -Phrase</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>257.39</v>
+        <v>2493.95</v>
       </c>
       <c r="E113" t="n">
-        <v>20</v>
+        <v>140</v>
       </c>
       <c r="F113" t="n">
-        <v>3064</v>
+        <v>25002</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>1795.76</v>
       </c>
       <c r="H113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Defensive</t>
+          <t>WM-SP-POS stand- Multi - PT</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0FN4FPJ83</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>135.68</v>
+        <v>10.04</v>
       </c>
       <c r="E114" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F114" t="n">
-        <v>1240</v>
+        <v>15</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3628,203 +3628,203 @@
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Defensive</t>
+          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0FN4D3C89</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>469.36</v>
+        <v>0</v>
       </c>
       <c r="E115" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="F115" t="n">
-        <v>5668</v>
+        <v>0</v>
       </c>
       <c r="G115" t="n">
-        <v>1694.07</v>
+        <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Defensive</t>
+          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0FN4DSQ6P</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>517.54</v>
+        <v>897.59</v>
       </c>
       <c r="E116" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F116" t="n">
-        <v>5793</v>
+        <v>8312</v>
       </c>
       <c r="G116" t="n">
-        <v>4744.07</v>
+        <v>1835.6</v>
       </c>
       <c r="H116" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Arms- Defensive</t>
+          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0FN4HDM6Z</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>77.34</v>
+        <v>485.56</v>
       </c>
       <c r="E117" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="F117" t="n">
-        <v>898</v>
+        <v>3144</v>
       </c>
       <c r="G117" t="n">
-        <v>2626.27</v>
+        <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - PT</t>
+          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0FHVWHQHR</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1575.26</v>
+        <v>6.68</v>
       </c>
       <c r="E118" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="F118" t="n">
-        <v>7211</v>
+        <v>837</v>
       </c>
       <c r="G118" t="n">
-        <v>11860.16</v>
+        <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - Phrase</t>
+          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0FN4D3C89</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>2509.5</v>
+        <v>293.98</v>
       </c>
       <c r="E119" t="n">
-        <v>122</v>
+        <v>37</v>
       </c>
       <c r="F119" t="n">
-        <v>8880</v>
+        <v>6387</v>
       </c>
       <c r="G119" t="n">
-        <v>8911.870000000001</v>
+        <v>1217.8</v>
       </c>
       <c r="H119" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 -Phrase</t>
+          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0FN4DSQ6P</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>2755.64</v>
+        <v>106.69</v>
       </c>
       <c r="E120" t="n">
-        <v>152</v>
+        <v>14</v>
       </c>
       <c r="F120" t="n">
-        <v>27077</v>
+        <v>4891</v>
       </c>
       <c r="G120" t="n">
-        <v>1795.76</v>
+        <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
-          <t>WM-SP-POS stand- Multi - PT</t>
+          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>B0FN4FPJ83</t>
+          <t>B0FHVWHQHR</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>10.04</v>
+        <v>68.55</v>
       </c>
       <c r="E121" t="n">
+        <v>4</v>
+      </c>
+      <c r="F121" t="n">
+        <v>1916</v>
+      </c>
+      <c r="G121" t="n">
+        <v>490.68</v>
+      </c>
+      <c r="H121" t="n">
         <v>1</v>
-      </c>
-      <c r="F121" t="n">
-        <v>18</v>
-      </c>
-      <c r="G121" t="n">
-        <v>0</v>
-      </c>
-      <c r="H121" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
+          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3833,26 +3833,26 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>0</v>
+        <v>199.35</v>
       </c>
       <c r="E122" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F122" t="n">
-        <v>0</v>
+        <v>1247</v>
       </c>
       <c r="G122" t="n">
-        <v>0</v>
+        <v>363.56</v>
       </c>
       <c r="H122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
+          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3861,26 +3861,26 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1042.42</v>
+        <v>1021.99</v>
       </c>
       <c r="E123" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="F123" t="n">
-        <v>8951</v>
+        <v>3073</v>
       </c>
       <c r="G123" t="n">
-        <v>2326.28</v>
+        <v>2944.08</v>
       </c>
       <c r="H123" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
+          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3889,13 +3889,13 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>598.99</v>
+        <v>499.62</v>
       </c>
       <c r="E124" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F124" t="n">
-        <v>3460</v>
+        <v>816</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3908,78 +3908,78 @@
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
+          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>B0FHVWHQHR</t>
+          <t>B0FN4D3C89</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>6.68</v>
+        <v>325.08</v>
       </c>
       <c r="E125" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="F125" t="n">
-        <v>864</v>
+        <v>4502</v>
       </c>
       <c r="G125" t="n">
-        <v>0</v>
+        <v>1090.68</v>
       </c>
       <c r="H125" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
+          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>B0FN4D3C89</t>
+          <t>B0FN4DSQ6P</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>449.69</v>
+        <v>588.25</v>
       </c>
       <c r="E126" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F126" t="n">
-        <v>8638</v>
+        <v>10288</v>
       </c>
       <c r="G126" t="n">
-        <v>1835.6</v>
+        <v>6378.84</v>
       </c>
       <c r="H126" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
+          <t>WM_SP_KT_Adjustable_Exact_Manual_HV</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>B0FN4DSQ6P</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>106.69</v>
+        <v>2770.94</v>
       </c>
       <c r="E127" t="n">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="F127" t="n">
-        <v>5077</v>
+        <v>80989</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3992,223 +3992,27 @@
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+          <t>White-B0FN81FD8M-monitor arm (high price)-SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>B0FHVWHQHR</t>
+          <t>B0FN81FD8M</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>68.55</v>
+        <v>122.41</v>
       </c>
       <c r="E128" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F128" t="n">
-        <v>1985</v>
+        <v>1616</v>
       </c>
       <c r="G128" t="n">
-        <v>490.68</v>
+        <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr"/>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>B0FN4D3C89</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>303.75</v>
-      </c>
-      <c r="E129" t="n">
-        <v>15</v>
-      </c>
-      <c r="F129" t="n">
-        <v>1920</v>
-      </c>
-      <c r="G129" t="n">
-        <v>727.12</v>
-      </c>
-      <c r="H129" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr"/>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>B0FN4DSQ6P</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>1056.31</v>
-      </c>
-      <c r="E130" t="n">
-        <v>36</v>
-      </c>
-      <c r="F130" t="n">
-        <v>3315</v>
-      </c>
-      <c r="G130" t="n">
-        <v>3434.76</v>
-      </c>
-      <c r="H130" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr"/>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>B0FN4HDM6Z</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>636.1899999999999</v>
-      </c>
-      <c r="E131" t="n">
-        <v>27</v>
-      </c>
-      <c r="F131" t="n">
-        <v>1033</v>
-      </c>
-      <c r="G131" t="n">
-        <v>1778.81</v>
-      </c>
-      <c r="H131" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr"/>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>B0FN4D3C89</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>563.4300000000001</v>
-      </c>
-      <c r="E132" t="n">
-        <v>50</v>
-      </c>
-      <c r="F132" t="n">
-        <v>6152</v>
-      </c>
-      <c r="G132" t="n">
-        <v>2727.12</v>
-      </c>
-      <c r="H132" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr"/>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>B0FN4DSQ6P</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>613.12</v>
-      </c>
-      <c r="E133" t="n">
-        <v>51</v>
-      </c>
-      <c r="F133" t="n">
-        <v>10704</v>
-      </c>
-      <c r="G133" t="n">
-        <v>6996.639999999999</v>
-      </c>
-      <c r="H133" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr"/>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>WM_SP_KT_Adjustable_Exact_Manual_HV</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>B0CPT3Q25C</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>3286.29</v>
-      </c>
-      <c r="E134" t="n">
-        <v>131</v>
-      </c>
-      <c r="F134" t="n">
-        <v>89428</v>
-      </c>
-      <c r="G134" t="n">
-        <v>12712.71</v>
-      </c>
-      <c r="H134" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr"/>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>White-B0FN81FD8M-monitor arm (high price)-SP-KT-Phrase</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>B0FN81FD8M</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>122.41</v>
-      </c>
-      <c r="E135" t="n">
-        <v>8</v>
-      </c>
-      <c r="F135" t="n">
-        <v>1616</v>
-      </c>
-      <c r="G135" t="n">
-        <v>0</v>
-      </c>
-      <c r="H135" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4505,13 +4309,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>308.28</v>
+        <v>185.19</v>
       </c>
       <c r="E10" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F10" t="n">
-        <v>14697</v>
+        <v>11117</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -4533,13 +4337,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>694.3199999999999</v>
+        <v>575.5599999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="F11" t="n">
-        <v>25298</v>
+        <v>20144</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -4617,13 +4421,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1049.38</v>
+        <v>964.92</v>
       </c>
       <c r="E14" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="F14" t="n">
-        <v>45404</v>
+        <v>43073</v>
       </c>
       <c r="G14" t="n">
         <v>2783.9</v>
@@ -4645,13 +4449,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>553.02</v>
+        <v>416.2</v>
       </c>
       <c r="E15" t="n">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="F15" t="n">
-        <v>21754</v>
+        <v>16976</v>
       </c>
       <c r="G15" t="n">
         <v>2626.27</v>
@@ -4755,7 +4559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4809,28 +4613,28 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Camb-SB-Branded-Phrase</t>
+          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>42</v>
+        <v>8525</v>
       </c>
       <c r="E2" t="n">
+        <v>85</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1009.66</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2626.27</v>
+      </c>
+      <c r="H2" t="n">
         <v>1</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2.708333333333333</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -4842,28 +4646,28 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Camb-SB-Branded-Phrase</t>
+          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B0BFVNS8HS</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>42</v>
+        <v>16044</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>177</v>
       </c>
       <c r="F3" t="n">
-        <v>2.708333333333333</v>
+        <v>2366.47</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>5579.66</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -4875,22 +4679,22 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Camb-SB-Branded-Phrase</t>
+          <t>WM-SB-Monitor Arms-Branded</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>2.708333333333333</v>
+        <v>4.718333333333333</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -4908,22 +4712,22 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Camb-SB-Branded-Phrase</t>
+          <t>WM-SB-Monitor Arms-Branded</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>2.708333333333333</v>
+        <v>4.718333333333333</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -4941,22 +4745,22 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Camb-SB-Branded-Phrase</t>
+          <t>WM-SB-Monitor Arms-Branded</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>2.708333333333333</v>
+        <v>4.718333333333333</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -4974,22 +4778,22 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Camb-SB-Branded-Phrase</t>
+          <t>WM-SB-Monitor Arms-Branded</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>2.708333333333333</v>
+        <v>4.718333333333333</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -5007,22 +4811,22 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Camb-SB-Defensive</t>
+          <t>WM-SB-Monitor Arms-Branded</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>655</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>139.0583333333333</v>
+        <v>4.718333333333333</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -5040,22 +4844,22 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Camb-SB-Defensive</t>
+          <t>WM-SB-Monitor Arms-Branded</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0BFVNS8HS</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>655</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>139.0583333333333</v>
+        <v>4.718333333333333</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -5073,28 +4877,28 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Camb-SB-Defensive</t>
+          <t>WM-SB-Monitor Arms-Defensive</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>655</v>
+        <v>2126</v>
       </c>
       <c r="E10" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F10" t="n">
-        <v>139.0583333333333</v>
+        <v>312.88</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2329.66</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -5106,723 +4910,30 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Camb-SB-Defensive</t>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>655</v>
+        <v>14852</v>
       </c>
       <c r="E11" t="n">
-        <v>13</v>
+        <v>124</v>
       </c>
       <c r="F11" t="n">
-        <v>139.0583333333333</v>
+        <v>2177.44</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>6988.98</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I11" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Camb-SB-Defensive</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>B0CPT3Q25C</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>655</v>
-      </c>
-      <c r="E12" t="n">
-        <v>13</v>
-      </c>
-      <c r="F12" t="n">
-        <v>139.0583333333333</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Camb-SB-Defensive</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>B0DQ4YWSMC</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>655</v>
-      </c>
-      <c r="E13" t="n">
-        <v>13</v>
-      </c>
-      <c r="F13" t="n">
-        <v>139.0583333333333</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>B0BFVMDJ2K</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>7316</v>
-      </c>
-      <c r="E14" t="n">
-        <v>298</v>
-      </c>
-      <c r="F14" t="n">
-        <v>692.4299999999999</v>
-      </c>
-      <c r="G14" t="n">
-        <v>39317.36</v>
-      </c>
-      <c r="H14" t="n">
-        <v>6</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>B0CPFS24ML</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>7316</v>
-      </c>
-      <c r="E15" t="n">
-        <v>298</v>
-      </c>
-      <c r="F15" t="n">
-        <v>692.4299999999999</v>
-      </c>
-      <c r="G15" t="n">
-        <v>39317.36</v>
-      </c>
-      <c r="H15" t="n">
-        <v>6</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>B0CPT3Q25C</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>3682</v>
-      </c>
-      <c r="E16" t="n">
-        <v>62</v>
-      </c>
-      <c r="F16" t="n">
-        <v>487.7133333333334</v>
-      </c>
-      <c r="G16" t="n">
-        <v>10875.98666666667</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>B0DQ1NV8D2</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>3682</v>
-      </c>
-      <c r="E17" t="n">
-        <v>62</v>
-      </c>
-      <c r="F17" t="n">
-        <v>487.7133333333334</v>
-      </c>
-      <c r="G17" t="n">
-        <v>10875.98666666667</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>B0DQ4YWSMC</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>3682</v>
-      </c>
-      <c r="E18" t="n">
-        <v>62</v>
-      </c>
-      <c r="F18" t="n">
-        <v>487.7133333333334</v>
-      </c>
-      <c r="G18" t="n">
-        <v>10875.98666666667</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>SB-Lshape-Multi Asin- KT- phrase</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>B0BFVMDJ2K</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>390</v>
-      </c>
-      <c r="E19" t="n">
-        <v>13</v>
-      </c>
-      <c r="F19" t="n">
-        <v>64.36</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1768.855</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>SB-Lshape-Multi Asin- KT- phrase</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>B0BFVNS8HS</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>390</v>
-      </c>
-      <c r="E20" t="n">
-        <v>13</v>
-      </c>
-      <c r="F20" t="n">
-        <v>64.36</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1768.855</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>SB-Lshape-Multi Asin- KT- phrase</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>B0BFW59TRG</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>390</v>
-      </c>
-      <c r="E21" t="n">
-        <v>13</v>
-      </c>
-      <c r="F21" t="n">
-        <v>64.36</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1768.855</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>SB-Lshape-Multi Asin- KT- phrase</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>B0BFWD6SNF</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>390</v>
-      </c>
-      <c r="E22" t="n">
-        <v>13</v>
-      </c>
-      <c r="F22" t="n">
-        <v>64.36</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1768.855</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>B0DP32F346</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>9999</v>
-      </c>
-      <c r="E23" t="n">
-        <v>105</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1265.03</v>
-      </c>
-      <c r="G23" t="n">
-        <v>5252.54</v>
-      </c>
-      <c r="H23" t="n">
-        <v>2</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>B0DP2WC5VW</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>19414</v>
-      </c>
-      <c r="E24" t="n">
-        <v>202</v>
-      </c>
-      <c r="F24" t="n">
-        <v>2717.31</v>
-      </c>
-      <c r="G24" t="n">
-        <v>5579.66</v>
-      </c>
-      <c r="H24" t="n">
-        <v>2</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>7</v>
-      </c>
-      <c r="E25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" t="n">
-        <v>4.718333333333333</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>B0DB5VVPSB</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>7</v>
-      </c>
-      <c r="E26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" t="n">
-        <v>4.718333333333333</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>B0DB5W4TCP</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>7</v>
-      </c>
-      <c r="E27" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" t="n">
-        <v>4.718333333333333</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>B0DB5YTQZV</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>7</v>
-      </c>
-      <c r="E28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" t="n">
-        <v>4.718333333333333</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>B0DP2Z5DQ9</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>7</v>
-      </c>
-      <c r="E29" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" t="n">
-        <v>4.718333333333333</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>B0DP32F346</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>7</v>
-      </c>
-      <c r="E30" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" t="n">
-        <v>4.718333333333333</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>WM-SB-Monitor Arms-Defensive</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>3803</v>
-      </c>
-      <c r="E31" t="n">
-        <v>57</v>
-      </c>
-      <c r="F31" t="n">
-        <v>613.13</v>
-      </c>
-      <c r="G31" t="n">
-        <v>2329.66</v>
-      </c>
-      <c r="H31" t="n">
-        <v>1</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>17299</v>
-      </c>
-      <c r="E32" t="n">
-        <v>140</v>
-      </c>
-      <c r="F32" t="n">
-        <v>2415.43</v>
-      </c>
-      <c r="G32" t="n">
-        <v>6988.98</v>
-      </c>
-      <c r="H32" t="n">
-        <v>4</v>
-      </c>
-      <c r="I32" t="inlineStr">
         <is>
           <t>White Mulberry</t>
         </is>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week23.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week23.xlsx
@@ -4559,7 +4559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4613,28 +4613,28 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
+          <t>Camb-SB-Branded-Phrase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8525</v>
+        <v>36</v>
       </c>
       <c r="E2" t="n">
-        <v>85</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>1009.66</v>
+        <v>2.708333333333333</v>
       </c>
       <c r="G2" t="n">
-        <v>2626.27</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -4646,28 +4646,28 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
+          <t>Camb-SB-Branded-Phrase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0BFVNS8HS</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16044</v>
+        <v>36</v>
       </c>
       <c r="E3" t="n">
-        <v>177</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>2366.47</v>
+        <v>2.708333333333333</v>
       </c>
       <c r="G3" t="n">
-        <v>5579.66</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -4679,22 +4679,22 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>Camb-SB-Branded-Phrase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>4.718333333333333</v>
+        <v>2.708333333333333</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -4712,22 +4712,22 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>Camb-SB-Branded-Phrase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>4.718333333333333</v>
+        <v>2.708333333333333</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -4745,22 +4745,22 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>Camb-SB-Branded-Phrase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>4.718333333333333</v>
+        <v>2.708333333333333</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -4778,22 +4778,22 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>Camb-SB-Branded-Phrase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>4.718333333333333</v>
+        <v>2.708333333333333</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>Camb-SB-Defensive</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D8" t="n">
+        <v>369</v>
+      </c>
+      <c r="E8" t="n">
         <v>6</v>
       </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
       <c r="F8" t="n">
-        <v>4.718333333333333</v>
+        <v>66.965</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -4844,22 +4844,22 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>Camb-SB-Defensive</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0BFVNS8HS</t>
         </is>
       </c>
       <c r="D9" t="n">
+        <v>369</v>
+      </c>
+      <c r="E9" t="n">
         <v>6</v>
       </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
       <c r="F9" t="n">
-        <v>4.718333333333333</v>
+        <v>66.965</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -4877,28 +4877,28 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Defensive</t>
+          <t>Camb-SB-Defensive</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2126</v>
+        <v>369</v>
       </c>
       <c r="E10" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="F10" t="n">
-        <v>312.88</v>
+        <v>66.965</v>
       </c>
       <c r="G10" t="n">
-        <v>2329.66</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -4910,30 +4910,591 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
+          <t>Camb-SB-Defensive</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>B0BFWD6SNF</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>369</v>
+      </c>
+      <c r="E11" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" t="n">
+        <v>66.965</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Camb-SB-Defensive</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>B0CPT3Q25C</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>369</v>
+      </c>
+      <c r="E12" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" t="n">
+        <v>66.965</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Camb-SB-Defensive</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>B0DQ4YWSMC</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>369</v>
+      </c>
+      <c r="E13" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" t="n">
+        <v>66.965</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>B0BFVMDJ2K</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2958</v>
+      </c>
+      <c r="E14" t="n">
+        <v>118</v>
+      </c>
+      <c r="F14" t="n">
+        <v>280.7993992273794</v>
+      </c>
+      <c r="G14" t="n">
+        <v>17680.69322386011</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>B0BFW59TRG</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1479</v>
+      </c>
+      <c r="E15" t="n">
+        <v>59</v>
+      </c>
+      <c r="F15" t="n">
+        <v>140.3996996136897</v>
+      </c>
+      <c r="G15" t="n">
+        <v>8840.346611930056</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>B0CPFS24ML</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>7527</v>
+      </c>
+      <c r="E16" t="n">
+        <v>301</v>
+      </c>
+      <c r="F16" t="n">
+        <v>714.6109011589308</v>
+      </c>
+      <c r="G16" t="n">
+        <v>44995.88016420983</v>
+      </c>
+      <c r="H16" t="n">
+        <v>6</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>B0DQ4YWSMC</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>9205</v>
+      </c>
+      <c r="E17" t="n">
+        <v>164</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1213.53</v>
+      </c>
+      <c r="G17" t="n">
+        <v>12712.71</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SB-Lshape-Multi Asin- KT- phrase</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>B0BFWD6SNF</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1560</v>
+      </c>
+      <c r="E18" t="n">
+        <v>53</v>
+      </c>
+      <c r="F18" t="n">
+        <v>257.44</v>
+      </c>
+      <c r="G18" t="n">
+        <v>7075.42</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>8525</v>
+      </c>
+      <c r="E19" t="n">
+        <v>85</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1009.66</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2626.27</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>B0DP2WC5VW</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>16044</v>
+      </c>
+      <c r="E20" t="n">
+        <v>177</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2366.47</v>
+      </c>
+      <c r="G20" t="n">
+        <v>5579.66</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>6</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4.718333333333333</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>B0DB5VVPSB</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>6</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>4.718333333333333</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>B0DB5W4TCP</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>6</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4.718333333333333</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>B0DB5YTQZV</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>6</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4.718333333333333</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>B0DP2Z5DQ9</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>6</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>4.718333333333333</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>6</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4.718333333333333</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Defensive</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>2126</v>
+      </c>
+      <c r="E27" t="n">
+        <v>31</v>
+      </c>
+      <c r="F27" t="n">
+        <v>312.88</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2329.66</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>B0DB5VG39T</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D28" t="n">
         <v>14852</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E28" t="n">
         <v>124</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F28" t="n">
         <v>2177.44</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G28" t="n">
         <v>6988.98</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H28" t="n">
         <v>4</v>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>White Mulberry</t>
         </is>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week23.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week23.xlsx
@@ -4559,7 +4559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5447,19 +5447,19 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2126</v>
+        <v>354</v>
       </c>
       <c r="E27" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="F27" t="n">
-        <v>312.88</v>
+        <v>52.14666666666667</v>
       </c>
       <c r="G27" t="n">
-        <v>2329.66</v>
+        <v>388.2766666666666</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -5471,30 +5471,195 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
+          <t>WM-SB-Monitor Arms-Defensive</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>B0DB5VVPSB</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>354</v>
+      </c>
+      <c r="E28" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>52.14666666666667</v>
+      </c>
+      <c r="G28" t="n">
+        <v>388.2766666666666</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Defensive</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>B0DB5W4TCP</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>354</v>
+      </c>
+      <c r="E29" t="n">
+        <v>5</v>
+      </c>
+      <c r="F29" t="n">
+        <v>52.14666666666667</v>
+      </c>
+      <c r="G29" t="n">
+        <v>388.2766666666666</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Defensive</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>B0DB5YTQZV</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>354</v>
+      </c>
+      <c r="E30" t="n">
+        <v>5</v>
+      </c>
+      <c r="F30" t="n">
+        <v>52.14666666666667</v>
+      </c>
+      <c r="G30" t="n">
+        <v>388.2766666666666</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Defensive</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>B0DP2Z5DQ9</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>354</v>
+      </c>
+      <c r="E31" t="n">
+        <v>5</v>
+      </c>
+      <c r="F31" t="n">
+        <v>52.14666666666667</v>
+      </c>
+      <c r="G31" t="n">
+        <v>388.2766666666666</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Defensive</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>354</v>
+      </c>
+      <c r="E32" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" t="n">
+        <v>52.14666666666667</v>
+      </c>
+      <c r="G32" t="n">
+        <v>388.2766666666666</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>B0DB5VG39T</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D33" t="n">
         <v>14852</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E33" t="n">
         <v>124</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F33" t="n">
         <v>2177.44</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G33" t="n">
         <v>6988.98</v>
       </c>
-      <c r="H28" t="n">
+      <c r="H33" t="n">
         <v>4</v>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>White Mulberry</t>
         </is>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week23.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week23.xlsx
@@ -4559,7 +4559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5447,19 +5447,19 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>354</v>
+        <v>2126</v>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="F27" t="n">
-        <v>52.14666666666667</v>
+        <v>312.88</v>
       </c>
       <c r="G27" t="n">
-        <v>388.2766666666666</v>
+        <v>2329.66</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -5471,195 +5471,30 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Defensive</t>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>354</v>
+        <v>14852</v>
       </c>
       <c r="E28" t="n">
-        <v>5</v>
+        <v>124</v>
       </c>
       <c r="F28" t="n">
-        <v>52.14666666666667</v>
+        <v>2177.44</v>
       </c>
       <c r="G28" t="n">
-        <v>388.2766666666666</v>
+        <v>6988.98</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I28" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>WM-SB-Monitor Arms-Defensive</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>B0DB5W4TCP</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>354</v>
-      </c>
-      <c r="E29" t="n">
-        <v>5</v>
-      </c>
-      <c r="F29" t="n">
-        <v>52.14666666666667</v>
-      </c>
-      <c r="G29" t="n">
-        <v>388.2766666666666</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>WM-SB-Monitor Arms-Defensive</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>B0DB5YTQZV</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>354</v>
-      </c>
-      <c r="E30" t="n">
-        <v>5</v>
-      </c>
-      <c r="F30" t="n">
-        <v>52.14666666666667</v>
-      </c>
-      <c r="G30" t="n">
-        <v>388.2766666666666</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>WM-SB-Monitor Arms-Defensive</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>B0DP2Z5DQ9</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>354</v>
-      </c>
-      <c r="E31" t="n">
-        <v>5</v>
-      </c>
-      <c r="F31" t="n">
-        <v>52.14666666666667</v>
-      </c>
-      <c r="G31" t="n">
-        <v>388.2766666666666</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>WM-SB-Monitor Arms-Defensive</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>B0DP32F346</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>354</v>
-      </c>
-      <c r="E32" t="n">
-        <v>5</v>
-      </c>
-      <c r="F32" t="n">
-        <v>52.14666666666667</v>
-      </c>
-      <c r="G32" t="n">
-        <v>388.2766666666666</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>14852</v>
-      </c>
-      <c r="E33" t="n">
-        <v>124</v>
-      </c>
-      <c r="F33" t="n">
-        <v>2177.44</v>
-      </c>
-      <c r="G33" t="n">
-        <v>6988.98</v>
-      </c>
-      <c r="H33" t="n">
-        <v>4</v>
-      </c>
-      <c r="I33" t="inlineStr">
         <is>
           <t>White Mulberry</t>
         </is>
